--- a/src/attributions/attributions_saliency_traj_479.xlsx
+++ b/src/attributions/attributions_saliency_traj_479.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2.361487713642418e-05</v>
+        <v>1.351142714156595e-06</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0001317484129685909</v>
+        <v>5.811270398226043e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.587531733093783e-05</v>
+        <v>3.843663307634415e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.491115108365193e-05</v>
+        <v>5.239812708168756e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.002752808039077e-05</v>
+        <v>5.728702490159776e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001535068440716714</v>
+        <v>2.10974098990846e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.818786353804171e-08</v>
+        <v>7.242276183205831e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1712383638951e-05</v>
+        <v>1.251114554179367e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.632824013446225e-06</v>
+        <v>1.681832628719349e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>5.252196569927037e-05</v>
+        <v>1.022242940962315e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>9.923391189659014e-05</v>
+        <v>1.269737595066545e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>8.624000656709541e-06</v>
+        <v>5.685478754458018e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>4.073935997439548e-06</v>
+        <v>2.722109684327734e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.017168506223243e-05</v>
+        <v>5.04725107930426e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001023940712912008</v>
+        <v>2.198305310230353e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.558740768814459e-05</v>
+        <v>1.169496840702777e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.411517536733299e-05</v>
+        <v>1.043612883222522e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>3.316661604912952e-05</v>
+        <v>5.524057087313849e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>7.632254892087076e-06</v>
+        <v>4.99631369166309e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.552373214508407e-05</v>
+        <v>1.148446699517081e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>5.710083314625081e-06</v>
+        <v>5.717159297091712e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.421304295945447e-05</v>
+        <v>8.106416089503909e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>4.004249058198184e-05</v>
+        <v>1.607630906619306e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.545768827782013e-05</v>
+        <v>1.426438984708511e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.055829488905147e-05</v>
+        <v>3.29644649355032e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.244640498043736e-05</v>
+        <v>2.958872755698394e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.766608758975053e-06</v>
+        <v>5.005595937745966e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.205689932248788e-05</v>
+        <v>8.715896626654285e-08</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.695844265574124e-06</v>
+        <v>1.568895129366865e-07</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.173133568954654e-05</v>
+        <v>3.857998933654017e-07</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.117888627457432e-05</v>
+        <v>1.130080136135803e-07</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.50225018337369e-05</v>
+        <v>2.791182396322256e-07</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.599981442268472e-05</v>
+        <v>1.828612283816256e-07</v>
       </c>
       <c r="AH4" t="n">
-        <v>5.809511549159652e-06</v>
+        <v>2.224012121132546e-07</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.832570655504242e-06</v>
+        <v>9.89015234154067e-07</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.214623464169563e-06</v>
+        <v>2.957137894554762e-07</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.91111644198827e-06</v>
+        <v>2.033881685292727e-07</v>
       </c>
       <c r="AL4" t="n">
-        <v>7.108092177077197e-06</v>
+        <v>2.463297619215155e-07</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.909860111481976e-05</v>
+        <v>7.4707457997647e-08</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.686812902335078e-05</v>
+        <v>6.702143764414359e-07</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.684509126993362e-06</v>
+        <v>8.810367830847099e-07</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.866846625693142e-05</v>
+        <v>2.318334395567945e-07</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.131192559318151e-05</v>
+        <v>5.131109048761573e-08</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.820840589061845e-05</v>
+        <v>3.619552444433793e-07</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.884829129674472e-05</v>
+        <v>1.719485851481295e-07</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.525765350786969e-06</v>
+        <v>4.437454492745019e-08</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.920892024529167e-05</v>
+        <v>2.126437266269932e-06</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.889225990860723e-05</v>
+        <v>3.448987797582959e-07</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.304924171563471e-05</v>
+        <v>2.2093942675383e-07</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.799224264686927e-05</v>
+        <v>8.805389484223269e-08</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.827510201721452e-05</v>
+        <v>1.275525164601277e-06</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.725317947100848e-05</v>
+        <v>6.751533874194138e-07</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.139902062481269e-05</v>
+        <v>9.072237503460201e-07</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.563628994626924e-05</v>
+        <v>8.929028183501941e-08</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.759688090416603e-05</v>
+        <v>1.101259840652347e-06</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.829715594998561e-05</v>
+        <v>2.546975963468867e-07</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.25464030134026e-05</v>
+        <v>1.817550554505942e-07</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.448742740554735e-06</v>
+        <v>4.414535510477435e-07</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.896852129197214e-05</v>
+        <v>6.901547067172942e-07</v>
       </c>
       <c r="BH4" t="n">
-        <v>6.505102646769956e-05</v>
+        <v>2.289202285510328e-07</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.639866918092594e-05</v>
+        <v>2.476672307238914e-07</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.608978527656291e-05</v>
+        <v>1.747638293636555e-06</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.38316237705294e-05</v>
+        <v>2.928410651747981e-07</v>
       </c>
       <c r="BL4" t="n">
-        <v>2.142085122613935e-06</v>
+        <v>2.3779223567999e-07</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.370428986381739e-06</v>
+        <v>7.44883209335967e-07</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.613581611716654e-07</v>
+        <v>3.092178957331271e-09</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.223286926688161e-05</v>
+        <v>4.60535375168547e-07</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.073424886679277e-05</v>
+        <v>2.783572199405171e-07</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.572725735371932e-08</v>
+        <v>2.070277673738019e-07</v>
       </c>
       <c r="BR4" t="n">
-        <v>1.584639721841086e-05</v>
+        <v>5.202273882787267e-07</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.211901331378613e-06</v>
+        <v>6.058214125914674e-07</v>
       </c>
       <c r="BT4" t="n">
-        <v>1.376660839014221e-05</v>
+        <v>2.893958708227728e-07</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.198717927763937e-05</v>
+        <v>3.531358174768684e-07</v>
       </c>
       <c r="BV4" t="n">
-        <v>3.221062797820196e-05</v>
+        <v>5.947564574171338e-08</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.064230284304358e-05</v>
+        <v>6.838925514784933e-07</v>
       </c>
       <c r="BX4" t="n">
-        <v>1.169800816569477e-05</v>
+        <v>1.258567408513045e-06</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.278553776908666e-05</v>
+        <v>1.294736080126313e-06</v>
       </c>
       <c r="BZ4" t="n">
-        <v>6.584322363778483e-06</v>
+        <v>1.694467869128857e-06</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.572098765085684e-06</v>
+        <v>1.479457409914176e-07</v>
       </c>
       <c r="CB4" t="n">
-        <v>5.735598733735969e-06</v>
+        <v>7.137178670291178e-08</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.18467612285167e-05</v>
+        <v>4.074800301623327e-07</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.879120413330384e-06</v>
+        <v>2.80358335658093e-07</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.565406455483753e-05</v>
+        <v>2.651964905453497e-07</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.207013337989338e-05</v>
+        <v>9.281512092229605e-08</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.34327978634974e-06</v>
+        <v>3.075591621382046e-07</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.105476258089766e-05</v>
+        <v>9.97411575553997e-08</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.757494985416997e-05</v>
+        <v>6.286293228185968e-07</v>
       </c>
       <c r="CJ4" t="n">
-        <v>7.653528882656246e-06</v>
+        <v>1.612172013665258e-07</v>
       </c>
       <c r="CK4" t="n">
-        <v>3.430386641412042e-08</v>
+        <v>1.971303333903052e-07</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.785837594070472e-05</v>
+        <v>1.292417692866366e-07</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.628393874852918e-05</v>
+        <v>1.193473622151942e-07</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.784836215141695e-05</v>
+        <v>1.209288143400045e-06</v>
       </c>
       <c r="CO4" t="n">
-        <v>2.618023609102238e-05</v>
+        <v>2.122711748597794e-07</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.489596797910053e-05</v>
+        <v>1.2512725788838e-07</v>
       </c>
       <c r="CQ4" t="n">
-        <v>8.609853466623463e-06</v>
+        <v>3.857090860037715e-07</v>
       </c>
       <c r="CR4" t="n">
-        <v>2.688411996132345e-06</v>
+        <v>8.702369882485073e-07</v>
       </c>
       <c r="CS4" t="n">
-        <v>1.33508237922797e-05</v>
+        <v>5.836633363287547e-07</v>
       </c>
       <c r="CT4" t="n">
-        <v>1.572016117279418e-06</v>
+        <v>4.287697947802371e-07</v>
       </c>
       <c r="CU4" t="n">
-        <v>3.550612746039405e-05</v>
+        <v>1.042360580072454e-07</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.146138856711332e-06</v>
+        <v>3.379399231562275e-07</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.13029434235068e-05</v>
+        <v>1.598540393388248e-07</v>
       </c>
       <c r="CX4" t="n">
-        <v>8.646603419038001e-06</v>
+        <v>1.733954135829663e-08</v>
       </c>
       <c r="CY4" t="n">
-        <v>5.128407337906538e-06</v>
+        <v>2.46127399350371e-07</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.351117862213869e-05</v>
+        <v>6.442512301418901e-08</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.750414205365814e-05</v>
+        <v>4.861118441112922e-07</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.60812669491861e-06</v>
+        <v>1.738264927553246e-07</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.994632723130053e-06</v>
+        <v>5.729587471137165e-08</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.781556784408167e-05</v>
+        <v>2.935326648412229e-08</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.157525184680708e-05</v>
+        <v>6.67122890263272e-07</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.068924848368624e-05</v>
+        <v>6.403063252946595e-07</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.279935349884909e-05</v>
+        <v>2.518439714549459e-07</v>
       </c>
       <c r="DH4" t="n">
-        <v>4.073083982802927e-05</v>
+        <v>6.078678893572942e-09</v>
       </c>
       <c r="DI4" t="n">
-        <v>1.615176734048873e-05</v>
+        <v>2.983148021939996e-07</v>
       </c>
       <c r="DJ4" t="n">
-        <v>7.540751539636403e-05</v>
+        <v>5.768594633082103e-07</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.398620174266398e-05</v>
+        <v>2.505160523469385e-07</v>
       </c>
       <c r="DL4" t="n">
-        <v>9.312593647337053e-06</v>
+        <v>1.491608685455503e-07</v>
       </c>
       <c r="DM4" t="n">
-        <v>5.91432471992448e-05</v>
+        <v>2.880703107166482e-07</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.401070039719343e-05</v>
+        <v>7.412229763303912e-08</v>
       </c>
       <c r="DO4" t="n">
-        <v>8.132425136864185e-06</v>
+        <v>3.300576167930558e-08</v>
       </c>
       <c r="DP4" t="n">
-        <v>3.936750545108225e-06</v>
+        <v>5.06760898133507e-07</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.333397995040286e-05</v>
+        <v>7.359804499174061e-07</v>
       </c>
       <c r="DR4" t="n">
-        <v>1.752242314978503e-05</v>
+        <v>5.533299258786428e-07</v>
       </c>
       <c r="DS4" t="n">
-        <v>6.064245553716319e-06</v>
+        <v>6.420592626454891e-07</v>
       </c>
       <c r="DT4" t="n">
-        <v>2.711920387810096e-05</v>
+        <v>5.168235475139227e-07</v>
       </c>
       <c r="DU4" t="n">
-        <v>7.626389560755342e-06</v>
+        <v>3.192894837411586e-07</v>
       </c>
       <c r="DV4" t="n">
-        <v>9.656458132667467e-06</v>
+        <v>1.865655008259637e-07</v>
       </c>
       <c r="DW4" t="n">
-        <v>1.07354962892714e-05</v>
+        <v>4.308398331431817e-07</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.584018698660657e-06</v>
+        <v>2.53625273671787e-07</v>
       </c>
       <c r="DY4" t="n">
-        <v>3.893005668942351e-06</v>
+        <v>5.164739036445098e-07</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1.03694292192813e-05</v>
+        <v>1.162529343901042e-07</v>
       </c>
       <c r="EA4" t="n">
-        <v>6.169520929688588e-06</v>
+        <v>3.79464125899176e-07</v>
       </c>
       <c r="EB4" t="n">
-        <v>4.480422830965836e-06</v>
+        <v>2.185006451327354e-07</v>
       </c>
       <c r="EC4" t="n">
-        <v>8.752749636187218e-06</v>
+        <v>1.551417909695374e-07</v>
       </c>
       <c r="ED4" t="n">
-        <v>1.422838158759987e-05</v>
+        <v>4.315368755669624e-07</v>
       </c>
       <c r="EE4" t="n">
-        <v>1.567812978464644e-05</v>
+        <v>5.76166144128365e-07</v>
       </c>
       <c r="EF4" t="n">
-        <v>7.085669494699687e-06</v>
+        <v>4.289592538953002e-07</v>
       </c>
       <c r="EG4" t="n">
-        <v>1.586475445947144e-05</v>
+        <v>3.795490215452446e-07</v>
       </c>
       <c r="EH4" t="n">
-        <v>5.10123527419637e-06</v>
+        <v>3.762791038752766e-07</v>
       </c>
       <c r="EI4" t="n">
-        <v>2.911353294621222e-05</v>
+        <v>3.323927728615672e-07</v>
       </c>
       <c r="EJ4" t="n">
-        <v>1.876280839496758e-05</v>
+        <v>4.765875587509072e-07</v>
       </c>
       <c r="EK4" t="n">
-        <v>5.83639666729141e-06</v>
+        <v>6.029121095707524e-07</v>
       </c>
       <c r="EL4" t="n">
-        <v>1.483298547100276e-05</v>
+        <v>4.917217566458021e-08</v>
       </c>
       <c r="EM4" t="n">
-        <v>1.672579628575477e-06</v>
+        <v>2.395855602799202e-08</v>
       </c>
       <c r="EN4" t="n">
-        <v>5.732156296289759e-06</v>
+        <v>2.140555181995296e-07</v>
       </c>
       <c r="EO4" t="n">
-        <v>1.028965107252588e-05</v>
+        <v>2.318783316468398e-07</v>
       </c>
       <c r="EP4" t="n">
-        <v>4.051398718729615e-06</v>
+        <v>8.579245047712902e-08</v>
       </c>
       <c r="EQ4" t="n">
-        <v>1.627542360438383e-06</v>
+        <v>7.000787149991083e-07</v>
       </c>
       <c r="ER4" t="n">
-        <v>6.309239324764349e-06</v>
+        <v>1.694375839633722e-07</v>
       </c>
       <c r="ES4" t="n">
-        <v>4.037112375954166e-05</v>
+        <v>2.283654794155154e-07</v>
       </c>
       <c r="ET4" t="n">
-        <v>5.234024865785614e-05</v>
+        <v>9.636531785872648e-07</v>
       </c>
       <c r="EU4" t="n">
-        <v>2.159308496629819e-05</v>
+        <v>2.867351156510267e-07</v>
       </c>
       <c r="EV4" t="n">
-        <v>1.948236240423284e-05</v>
+        <v>2.067714035547397e-07</v>
       </c>
       <c r="EW4" t="n">
-        <v>3.360501796123572e-05</v>
+        <v>5.674850811487886e-09</v>
       </c>
       <c r="EX4" t="n">
-        <v>1.508484274381772e-06</v>
+        <v>4.171811269770842e-07</v>
       </c>
       <c r="EY4" t="n">
-        <v>2.115698225679807e-05</v>
+        <v>2.82276715779517e-07</v>
       </c>
       <c r="EZ4" t="n">
-        <v>2.622875399538316e-06</v>
+        <v>6.935501062343974e-08</v>
       </c>
       <c r="FA4" t="n">
-        <v>2.147476152458694e-06</v>
+        <v>3.337857492624607e-07</v>
       </c>
       <c r="FB4" t="n">
-        <v>1.67839607456699e-05</v>
+        <v>6.372349048433534e-08</v>
       </c>
       <c r="FC4" t="n">
-        <v>2.123187368852086e-05</v>
+        <v>6.399482685992552e-07</v>
       </c>
       <c r="FD4" t="n">
-        <v>1.256631549040321e-05</v>
+        <v>1.489090948325611e-07</v>
       </c>
       <c r="FE4" t="n">
-        <v>6.003120688546915e-06</v>
+        <v>1.454122013910819e-07</v>
       </c>
       <c r="FF4" t="n">
-        <v>2.494253203622065e-05</v>
+        <v>2.172765434238499e-08</v>
       </c>
       <c r="FG4" t="n">
-        <v>1.08604626802844e-05</v>
+        <v>6.018996714374225e-07</v>
       </c>
       <c r="FH4" t="n">
-        <v>1.301046722801402e-05</v>
+        <v>7.137757052078086e-08</v>
       </c>
       <c r="FI4" t="n">
-        <v>1.286244423681637e-05</v>
+        <v>2.165065211556794e-07</v>
       </c>
       <c r="FJ4" t="n">
-        <v>2.257064625155181e-05</v>
+        <v>3.64093040161606e-08</v>
       </c>
       <c r="FK4" t="n">
-        <v>8.715602234588005e-06</v>
+        <v>7.862194593144523e-07</v>
       </c>
       <c r="FL4" t="n">
-        <v>2.633531403262168e-05</v>
+        <v>4.379948563837388e-07</v>
       </c>
       <c r="FM4" t="n">
-        <v>8.020558198040817e-06</v>
+        <v>2.304994239921143e-08</v>
       </c>
       <c r="FN4" t="n">
-        <v>8.496015652781352e-06</v>
+        <v>1.840571428601834e-07</v>
       </c>
       <c r="FO4" t="n">
-        <v>1.531028829049319e-05</v>
+        <v>4.416684191710374e-07</v>
       </c>
       <c r="FP4" t="n">
-        <v>4.896092832495924e-06</v>
+        <v>9.123904192165355e-07</v>
       </c>
       <c r="FQ4" t="n">
-        <v>3.281826866441406e-05</v>
+        <v>6.11471534739394e-07</v>
       </c>
       <c r="FR4" t="n">
-        <v>1.75089189724531e-05</v>
+        <v>2.324171362033667e-07</v>
       </c>
       <c r="FS4" t="n">
-        <v>3.6559267755365e-06</v>
+        <v>1.864861047806698e-07</v>
       </c>
       <c r="FT4" t="n">
-        <v>2.114313974743709e-05</v>
+        <v>2.254597575301887e-06</v>
       </c>
       <c r="FU4" t="n">
-        <v>4.3736923544202e-05</v>
+        <v>5.072663498140173e-07</v>
       </c>
       <c r="FV4" t="n">
-        <v>8.735420124139637e-06</v>
+        <v>8.23731852506171e-07</v>
       </c>
       <c r="FW4" t="n">
-        <v>1.912541119963862e-05</v>
+        <v>5.788023713648727e-07</v>
       </c>
       <c r="FX4" t="n">
-        <v>2.255897925351746e-05</v>
+        <v>5.173227464183583e-07</v>
       </c>
       <c r="FY4" t="n">
-        <v>2.200513699790463e-05</v>
+        <v>3.071295395784546e-08</v>
       </c>
       <c r="FZ4" t="n">
-        <v>1.849006912379991e-05</v>
+        <v>7.318266170841525e-07</v>
       </c>
       <c r="GA4" t="n">
-        <v>3.19428181683179e-06</v>
+        <v>5.805612772746827e-07</v>
       </c>
       <c r="GB4" t="n">
-        <v>1.539665390737355e-05</v>
+        <v>1.518495480468118e-07</v>
       </c>
       <c r="GC4" t="n">
-        <v>3.950471000280231e-05</v>
+        <v>6.767412514818716e-07</v>
       </c>
       <c r="GD4" t="n">
-        <v>3.199411651166884e-07</v>
+        <v>5.446008799481206e-07</v>
       </c>
       <c r="GE4" t="n">
-        <v>8.577392691222485e-06</v>
+        <v>1.956477575504323e-07</v>
       </c>
       <c r="GF4" t="n">
-        <v>5.862189937033691e-06</v>
+        <v>3.824762870863196e-07</v>
       </c>
       <c r="GG4" t="n">
-        <v>1.844491634983569e-05</v>
+        <v>1.194334799947683e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0005602577002719045</v>
+        <v>0.002261453773826361</v>
       </c>
       <c r="B5" t="n">
-        <v>0.008447646163403988</v>
+        <v>0.05415469408035278</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00121621263679117</v>
+        <v>0.009534499607980251</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004630964249372482</v>
+        <v>0.03918647021055222</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005709308199584484</v>
+        <v>0.001209713169373572</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001734267803840339</v>
+        <v>0.001788847497664392</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001157650258392096</v>
+        <v>0.0323498323559761</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0006243273383006454</v>
+        <v>0.01893296092748642</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0004330635129008442</v>
+        <v>0.01239548064768314</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001486706314608455</v>
+        <v>0.007525566965341568</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006449965760111809</v>
+        <v>0.04926829412579536</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006759938551113009</v>
+        <v>0.01642013341188431</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004774127155542374</v>
+        <v>0.05444278940558434</v>
       </c>
       <c r="N5" t="n">
-        <v>0.007952864281833172</v>
+        <v>0.01914523355662823</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00241393712349236</v>
+        <v>0.005217680707573891</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001153579214587808</v>
+        <v>0.02890485897660255</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002852951874956489</v>
+        <v>0.00265860790386796</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0007386321667581797</v>
+        <v>0.006282595451921225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001722053857520223</v>
+        <v>0.002413979731500149</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001913827378302813</v>
+        <v>0.008146208710968494</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001262381440028548</v>
+        <v>6.566324736922979e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001760199957061559</v>
+        <v>0.0004540695808827877</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003075808053836226</v>
+        <v>0.006996407639235258</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001814448740333319</v>
+        <v>0.01172009669244289</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001145595568232238</v>
+        <v>0.005660479888319969</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001360836322419345</v>
+        <v>0.01833124458789825</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0002596343110781163</v>
+        <v>0.004453730769455433</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001782733132131398</v>
+        <v>2.807658165693283e-05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0008845990523695946</v>
+        <v>0.002105109393596649</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.001011850428767502</v>
+        <v>0.006770421750843525</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0009972176048904657</v>
+        <v>0.006012562196701765</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.001821293961256742</v>
+        <v>0.006070696283131838</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0007001954363659024</v>
+        <v>0.03104126825928688</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0001103395916288719</v>
+        <v>0.003216675715520978</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.000382712110877037</v>
+        <v>0.01261336356401443</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.001395541708916426</v>
+        <v>0.002951858332380652</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0002983552403748035</v>
+        <v>0.002783660776913166</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0004776033747475594</v>
+        <v>0.01849616505205631</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0003817163524217904</v>
+        <v>0.007259415462613106</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0002747047110460699</v>
+        <v>0.004755686968564987</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.00261327950283885</v>
+        <v>0.01182530727237463</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.001646007527597249</v>
+        <v>0.008848457597196102</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0001578006485942751</v>
+        <v>0.008121653459966183</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0001050237624440342</v>
+        <v>0.0008639605366624892</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.092508556321263e-06</v>
+        <v>0.002648007357493043</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0003196086909156293</v>
+        <v>7.822795305401087e-05</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.005970338359475136</v>
+        <v>0.02153537981212139</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0004061980871483684</v>
+        <v>0.007956227287650108</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0004461506032384932</v>
+        <v>0.01855452731251717</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001153525430709124</v>
+        <v>0.03951485082507133</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0006055533303879201</v>
+        <v>0.01290619745850563</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0004283848393242806</v>
+        <v>0.002124019665643573</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0004011341952718794</v>
+        <v>0.001425221329554915</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.002642966574057937</v>
+        <v>0.006127859465777874</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.001177239464595914</v>
+        <v>0.009868554770946503</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.00324986083433032</v>
+        <v>0.001094247912988067</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.002409169217571616</v>
+        <v>0.01029867865145206</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.00193829508498311</v>
+        <v>0.00541978795081377</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.005024265497922897</v>
+        <v>0.01843432150781155</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.003639279399067163</v>
+        <v>0.002711608773097396</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.001586395897902548</v>
+        <v>0.01270363666117191</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0003528479719534516</v>
+        <v>0.02557198703289032</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.001352567691355944</v>
+        <v>0.003305954392999411</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.001419855398125947</v>
+        <v>0.0002756944159045815</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.002824776340276003</v>
+        <v>0.01098028570413589</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.001265386934392154</v>
+        <v>0.00574542535468936</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.000951319991145283</v>
+        <v>0.009077451191842556</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.003148447256535292</v>
+        <v>0.01111239194869995</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.002153454115614295</v>
+        <v>0.001256446819752455</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0005793935270048678</v>
+        <v>0.004660632461309433</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.001392736565321684</v>
+        <v>0.003969017416238785</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.001024798955768347</v>
+        <v>0.008293847553431988</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0003252688911743462</v>
+        <v>0.003093754639849067</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.002316663041710854</v>
+        <v>0.01883724704384804</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0007523961248807609</v>
+        <v>0.007740397937595844</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0001205249864142388</v>
+        <v>0.02995745837688446</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0008507100865244865</v>
+        <v>0.002339770086109638</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.001634697546251118</v>
+        <v>0.008223041892051697</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.000190212536836043</v>
+        <v>0.006731519009917974</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0006089364178478718</v>
+        <v>0.003488277783617377</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.00100778613705188</v>
+        <v>0.001165589550510049</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0001153112534666434</v>
+        <v>0.0006432950031012297</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.001400836859829724</v>
+        <v>0.0169681292027235</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0001113094913307577</v>
+        <v>0.0008676091674715281</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0004286525654606521</v>
+        <v>0.0178074985742569</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0003344187862239778</v>
+        <v>0.002752524800598621</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0002836736384779215</v>
+        <v>0.001152500743046403</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0003700804663822055</v>
+        <v>0.001861680415458977</v>
       </c>
       <c r="CK5" t="n">
-        <v>2.719901385717094e-05</v>
+        <v>0.0004409214307088405</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0009774956852197647</v>
+        <v>0.002173094544559717</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.00194672285579145</v>
+        <v>0.004601056687533855</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.001894261222332716</v>
+        <v>0.003169687930494547</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0001677726686466485</v>
+        <v>0.022311145439744</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.001676571322605014</v>
+        <v>0.03682380542159081</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.002299906685948372</v>
+        <v>0.004093952011317015</v>
       </c>
       <c r="CR5" t="n">
-        <v>2.175639383494854e-05</v>
+        <v>0.01246107555925846</v>
       </c>
       <c r="CS5" t="n">
-        <v>1.2303760740906e-05</v>
+        <v>0.01648441888391972</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.001675138249993324</v>
+        <v>0.01058825943619013</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0007711293874308467</v>
+        <v>0.004241053480654955</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.161036198027432e-05</v>
+        <v>0.0005533647490665317</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0009518440347164869</v>
+        <v>0.01626522839069366</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0005058130482211709</v>
+        <v>0.00241377716884017</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.000493632978759706</v>
+        <v>0.01896589994430542</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0002887834561988711</v>
+        <v>0.0003659976064227521</v>
       </c>
       <c r="DA5" t="n">
-        <v>7.986105629242957e-05</v>
+        <v>0.0005849354201927781</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0002115634706569836</v>
+        <v>0.0012268943246454</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0004073953605256975</v>
+        <v>0.0004725983599200845</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0005403203540481627</v>
+        <v>0.000639003817923367</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.001278392970561981</v>
+        <v>0.001188277266919613</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.002158621791750193</v>
+        <v>0.01308061461895704</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.002092669950798154</v>
+        <v>0.003223533742129803</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.003267103806138039</v>
+        <v>0.02273096144199371</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.001940736197866499</v>
+        <v>0.007181842811405659</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.001051739673130214</v>
+        <v>0.01746424660086632</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.64674410270527e-05</v>
+        <v>0.004754397552460432</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.001335994224064052</v>
+        <v>0.0291586946696043</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0001807602384360507</v>
+        <v>0.003519314341247082</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.000507415272295475</v>
+        <v>0.00103806285187602</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0008548526093363762</v>
+        <v>0.00646555982530117</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0006706435233354568</v>
+        <v>0.001933443825691938</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0001699816784821451</v>
+        <v>0.01036108750849962</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0006784299039281905</v>
+        <v>3.940809983760118e-05</v>
       </c>
       <c r="DS5" t="n">
-        <v>1.896674802992493e-05</v>
+        <v>0.002060398226603866</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0009404205484315753</v>
+        <v>0.01209287811070681</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0004299407009966671</v>
+        <v>0.003971519414335489</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.00178128236439079</v>
+        <v>0.02720814943313599</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0004029679985251278</v>
+        <v>0.0007684436859562993</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0009916054550558329</v>
+        <v>0.0008773145964369178</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0005336628528311849</v>
+        <v>0.01188455522060394</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0005261246114969254</v>
+        <v>0.0006743031553924084</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0009782196721062064</v>
+        <v>0.004090182948857546</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.002360476879402995</v>
+        <v>0.004877280909568071</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0005942550487816334</v>
+        <v>0.003126313909888268</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0006103613413870335</v>
+        <v>0.03106678649783134</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0004577683284878731</v>
+        <v>0.01992661133408546</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0003585987724363804</v>
+        <v>0.008577954024076462</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.001071283943019807</v>
+        <v>0.01389895752072334</v>
       </c>
       <c r="EH5" t="n">
-        <v>5.128221891936846e-05</v>
+        <v>0.007601634599268436</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.00113460945431143</v>
+        <v>0.0224659126251936</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.001812210772186518</v>
+        <v>0.006603614427149296</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0001393446000292897</v>
+        <v>0.005953532177954912</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.001172207877971232</v>
+        <v>0.002262564841657877</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.000302000786177814</v>
+        <v>0.004497301764786243</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0006547911325469613</v>
+        <v>0.002216967288404703</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0007923060329630971</v>
+        <v>0.002923957072198391</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.001129842945374548</v>
+        <v>0.02141231670975685</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0001781095488695428</v>
+        <v>0.006914634257555008</v>
       </c>
       <c r="ER5" t="n">
-        <v>1.210220216307789e-05</v>
+        <v>0.01131943240761757</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0005851799505762756</v>
+        <v>0.001311516272835433</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0007612792542204261</v>
+        <v>0.006929904222488403</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0001712525845505297</v>
+        <v>0.007744640111923218</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0009955131681635976</v>
+        <v>0.002684555016458035</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.000748062040656805</v>
+        <v>0.008002135902643204</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0004535792395472527</v>
+        <v>0.0003969025274273008</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.001196385943330824</v>
+        <v>0.01692648604512215</v>
       </c>
       <c r="EZ5" t="n">
-        <v>2.74875528702978e-05</v>
+        <v>0.001721241162158549</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0005178343853913248</v>
+        <v>0.0233800858259201</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0008365549147129059</v>
+        <v>0.0008347881375811994</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0006024697795510292</v>
+        <v>0.0006934514385648072</v>
       </c>
       <c r="FD5" t="n">
-        <v>6.630129792029038e-05</v>
+        <v>0.0003875913680531085</v>
       </c>
       <c r="FE5" t="n">
-        <v>2.727580431383103e-05</v>
+        <v>0.0006357161910273135</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.000420785479946062</v>
+        <v>0.002358381170779467</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0004758373543154448</v>
+        <v>0.005831895396113396</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.001333325635641813</v>
+        <v>0.005821134429425001</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0008952224161475897</v>
+        <v>0.007257664576172829</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.001126599148847163</v>
+        <v>0.01538379676640034</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.001051665749400854</v>
+        <v>0.00669338321313262</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.001507565146312118</v>
+        <v>0.005298798903822899</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0005083510186523199</v>
+        <v>0.001551098190248013</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0004057421465404332</v>
+        <v>0.00964463222771883</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0001196176744997501</v>
+        <v>0.004780636634677649</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.000836376566439867</v>
+        <v>0.01048636063933372</v>
       </c>
       <c r="FQ5" t="n">
-        <v>7.037392788333818e-05</v>
+        <v>0.02214855328202248</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0009306714637205005</v>
+        <v>0.001610592007637024</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.000797236105427146</v>
+        <v>0.004487001802772284</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.001961828442290425</v>
+        <v>0.01887906342744827</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.001245583989657462</v>
+        <v>0.0154122319072485</v>
       </c>
       <c r="FV5" t="n">
-        <v>1.232529757544398e-05</v>
+        <v>0.005016165785491467</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.001873715780675411</v>
+        <v>0.005586543586105108</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0001155344798462465</v>
+        <v>0.02312208525836468</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.001142532913945615</v>
+        <v>0.005877065472304821</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0009323042468167841</v>
+        <v>0.00487821688875556</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.001242954866029322</v>
+        <v>0.007214038167148829</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0005850096931681037</v>
+        <v>0.02314173802733421</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.002129652770236135</v>
+        <v>0.000260327011346817</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.001278301002457738</v>
+        <v>0.003974632360041142</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0005369535647332668</v>
+        <v>0.01066399086266756</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.001586380880326033</v>
+        <v>0.001073879655450583</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.001530102919787169</v>
+        <v>0.0007857165765017271</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0001515386538812891</v>
+        <v>7.502471679934203e-14</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0001051341605489142</v>
+        <v>2.135214477016339e-13</v>
       </c>
       <c r="C6" t="n">
-        <v>4.624521534424275e-05</v>
+        <v>4.916934101626552e-14</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001193391071865335</v>
+        <v>3.136729699766694e-14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0004589187446981668</v>
+        <v>1.347666824056543e-13</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0003445464826654643</v>
+        <v>3.242752746011879e-13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001875088200904429</v>
+        <v>2.536315341777895e-13</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001087675409507938</v>
+        <v>5.508664813365372e-13</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003606410755310208</v>
+        <v>9.012030759234652e-15</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001991361787077039</v>
+        <v>9.810301036155059e-14</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001904642849694937</v>
+        <v>6.528927246930716e-14</v>
       </c>
       <c r="L6" t="n">
-        <v>2.177587521146052e-05</v>
+        <v>1.294974598473747e-13</v>
       </c>
       <c r="M6" t="n">
-        <v>4.674814408645034e-05</v>
+        <v>5.658852970632025e-14</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0004979752702638507</v>
+        <v>2.897433811974159e-13</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002675219438970089</v>
+        <v>3.718848688195886e-13</v>
       </c>
       <c r="P6" t="n">
-        <v>6.437860429286957e-05</v>
+        <v>4.388669061407974e-13</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.060984868672676e-05</v>
+        <v>5.07730684752572e-13</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001022579526761547</v>
+        <v>5.869255277103635e-14</v>
       </c>
       <c r="S6" t="n">
-        <v>8.562183211324736e-05</v>
+        <v>3.962004064671926e-14</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001051532090059482</v>
+        <v>1.564629773399134e-13</v>
       </c>
       <c r="U6" t="n">
-        <v>3.832984293694608e-05</v>
+        <v>7.736856538461193e-15</v>
       </c>
       <c r="V6" t="n">
-        <v>1.344782685919199e-05</v>
+        <v>7.121224183254116e-14</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001728369097691029</v>
+        <v>2.884805567170134e-13</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001280470896745101</v>
+        <v>1.667245019750267e-15</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.944986620917916e-05</v>
+        <v>1.044643972020198e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.605326881166548e-05</v>
+        <v>3.28542016725733e-13</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001614898792468011</v>
+        <v>1.028263693132357e-14</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.312162905582227e-08</v>
+        <v>8.419763638470995e-14</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.000198082227143459</v>
+        <v>1.024789926312372e-13</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0001281836157431826</v>
+        <v>1.148154176442741e-14</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0001007372629828751</v>
+        <v>3.998463073227182e-15</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0004115006886422634</v>
+        <v>1.264408093200678e-13</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0003522614715620875</v>
+        <v>2.158898195847928e-13</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0002669235982466489</v>
+        <v>8.021131637581461e-14</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.000129541804199107</v>
+        <v>1.259816903576017e-13</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0002160318254027516</v>
+        <v>1.357681667286427e-14</v>
       </c>
       <c r="AK6" t="n">
-        <v>6.104796193540096e-05</v>
+        <v>1.955072490348025e-14</v>
       </c>
       <c r="AL6" t="n">
-        <v>9.695249173091725e-05</v>
+        <v>4.137712579250358e-14</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.400328958174214e-05</v>
+        <v>1.829011456720188e-14</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.000223975905100815</v>
+        <v>4.324140803996061e-14</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0001430755364708602</v>
+        <v>1.309285525049469e-13</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.500396607909352e-05</v>
+        <v>4.038992583313764e-14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0001641325943637639</v>
+        <v>6.636973414429759e-14</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0001207818495458923</v>
+        <v>9.231752461005133e-14</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.186648922972381e-05</v>
+        <v>6.292064308813239e-14</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.244174437597394e-05</v>
+        <v>5.549441386022008e-15</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.740163709968328e-05</v>
+        <v>2.938291699793733e-13</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.811896987026557e-05</v>
+        <v>1.527017038207082e-13</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0001289664651267231</v>
+        <v>1.32549624488193e-13</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0003246398409828544</v>
+        <v>1.526397416665506e-13</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0001833066780818626</v>
+        <v>3.599109400266587e-13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0004789261729456484</v>
+        <v>6.251371490774427e-14</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0002136511175194755</v>
+        <v>1.890948606465132e-13</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0001386242947774008</v>
+        <v>1.007509776562027e-14</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0001976634957827628</v>
+        <v>9.940119338530326e-14</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0001743557804729789</v>
+        <v>2.71434784371305e-13</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.30117405205965e-06</v>
+        <v>4.315653533864573e-14</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.358253939542919e-05</v>
+        <v>1.379645638184546e-13</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0004296578117646277</v>
+        <v>8.393149185641907e-14</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0003238966164644808</v>
+        <v>1.477947809708918e-13</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0001322191383223981</v>
+        <v>4.725078767381201e-14</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0001313782122451812</v>
+        <v>4.483827859783768e-13</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0002182941971113905</v>
+        <v>5.526886253889342e-14</v>
       </c>
       <c r="BL6" t="n">
-        <v>4.015493323095143e-05</v>
+        <v>1.040266912324603e-13</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0001630381884751841</v>
+        <v>5.586114185693151e-14</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0001080247166100889</v>
+        <v>3.116915227438163e-14</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0002465974539518356</v>
+        <v>3.566658551617738e-14</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.211960185784847e-05</v>
+        <v>1.147023556864746e-13</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.513679495081306e-05</v>
+        <v>5.313209318043646e-14</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0002298487816005945</v>
+        <v>3.824377812588868e-14</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.537271757319104e-05</v>
+        <v>1.97318256298009e-14</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0001641568669583648</v>
+        <v>7.127153413884896e-14</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.675833431771025e-05</v>
+        <v>1.044363163657525e-14</v>
       </c>
       <c r="BV6" t="n">
-        <v>2.883619526983239e-05</v>
+        <v>2.009465727495496e-14</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.074883564608172e-05</v>
+        <v>7.695900801395553e-15</v>
       </c>
       <c r="BX6" t="n">
-        <v>8.242550393333659e-05</v>
+        <v>2.207029182891077e-13</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0001797229197109118</v>
+        <v>1.909059255079601e-13</v>
       </c>
       <c r="BZ6" t="n">
-        <v>7.932590960990638e-06</v>
+        <v>6.014568861402794e-14</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0001236188400071114</v>
+        <v>4.17453072977525e-15</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0001036219546222128</v>
+        <v>9.457507747865496e-14</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0001032749569276348</v>
+        <v>1.493619782705607e-14</v>
       </c>
       <c r="CD6" t="n">
-        <v>1.198390054923948e-05</v>
+        <v>3.151860757523266e-14</v>
       </c>
       <c r="CE6" t="n">
-        <v>3.071196988457814e-05</v>
+        <v>3.29078669696059e-14</v>
       </c>
       <c r="CF6" t="n">
-        <v>5.18744345754385e-05</v>
+        <v>1.383209292140893e-14</v>
       </c>
       <c r="CG6" t="n">
-        <v>8.186572813428938e-05</v>
+        <v>1.663072111935619e-14</v>
       </c>
       <c r="CH6" t="n">
-        <v>8.968590918811969e-06</v>
+        <v>1.323436802855293e-14</v>
       </c>
       <c r="CI6" t="n">
-        <v>9.55532868829323e-06</v>
+        <v>6.744829846548617e-14</v>
       </c>
       <c r="CJ6" t="n">
-        <v>6.195183959789574e-05</v>
+        <v>2.691920511911465e-14</v>
       </c>
       <c r="CK6" t="n">
-        <v>4.23059864260722e-05</v>
+        <v>3.07650362433784e-14</v>
       </c>
       <c r="CL6" t="n">
-        <v>8.836139750201255e-05</v>
+        <v>8.822775816137371e-14</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.698595224297605e-05</v>
+        <v>1.128269298735635e-13</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0001043096272042021</v>
+        <v>1.090023118424308e-13</v>
       </c>
       <c r="CO6" t="n">
-        <v>5.487828093464486e-05</v>
+        <v>1.060839919598058e-13</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0002001262328121811</v>
+        <v>1.244998705908842e-13</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.000224350776989013</v>
+        <v>5.995602777274234e-14</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.124878963310039e-05</v>
+        <v>1.03689782183624e-13</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0001166768051916733</v>
+        <v>2.80202618919978e-13</v>
       </c>
       <c r="CT6" t="n">
-        <v>8.488327875966206e-05</v>
+        <v>1.109497625609128e-13</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0004366500361356884</v>
+        <v>1.769851219789523e-13</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.845177732524462e-06</v>
+        <v>2.190836149106555e-14</v>
       </c>
       <c r="CW6" t="n">
-        <v>4.382991392049007e-05</v>
+        <v>2.10720180996056e-14</v>
       </c>
       <c r="CX6" t="n">
-        <v>9.520437743049115e-06</v>
+        <v>1.988812523142595e-14</v>
       </c>
       <c r="CY6" t="n">
-        <v>7.325829938054085e-05</v>
+        <v>1.514656692983615e-14</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.876264261431061e-05</v>
+        <v>7.378240406879025e-14</v>
       </c>
       <c r="DA6" t="n">
-        <v>4.164447818766348e-05</v>
+        <v>9.350106003032724e-14</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.591867476236075e-05</v>
+        <v>5.534386561230689e-14</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.404634506092407e-05</v>
+        <v>2.6233343906998e-14</v>
       </c>
       <c r="DD6" t="n">
-        <v>7.444187940564007e-05</v>
+        <v>8.062570522240214e-14</v>
       </c>
       <c r="DE6" t="n">
-        <v>9.720143862068653e-05</v>
+        <v>2.262714213045747e-13</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0002234866551589221</v>
+        <v>3.101933044192401e-13</v>
       </c>
       <c r="DG6" t="n">
-        <v>4.619554965756834e-05</v>
+        <v>1.388996746396962e-13</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.0002360477519687265</v>
+        <v>1.610370094651953e-13</v>
       </c>
       <c r="DI6" t="n">
-        <v>9.312963811680675e-06</v>
+        <v>4.724421131000953e-14</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0004520314978435636</v>
+        <v>3.743769617231552e-13</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0001966790587175637</v>
+        <v>3.397076118127028e-14</v>
       </c>
       <c r="DL6" t="n">
-        <v>7.737401756457984e-05</v>
+        <v>1.53077081717877e-13</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0003545575891621411</v>
+        <v>3.409398414630505e-14</v>
       </c>
       <c r="DN6" t="n">
-        <v>6.147401290945709e-05</v>
+        <v>1.84273833713812e-13</v>
       </c>
       <c r="DO6" t="n">
-        <v>4.149811138631776e-05</v>
+        <v>1.486014951498568e-14</v>
       </c>
       <c r="DP6" t="n">
-        <v>1.846361919888295e-05</v>
+        <v>2.520908795025558e-14</v>
       </c>
       <c r="DQ6" t="n">
-        <v>2.650569513207301e-05</v>
+        <v>2.951964573390947e-13</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0003249809960834682</v>
+        <v>2.016986566915485e-13</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.0001842463243519887</v>
+        <v>1.015255587932806e-13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.0002775818866211921</v>
+        <v>1.415459546447173e-13</v>
       </c>
       <c r="DU6" t="n">
-        <v>4.355489181762096e-06</v>
+        <v>8.614907832243945e-14</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.0003378779219929129</v>
+        <v>2.205187258925295e-14</v>
       </c>
       <c r="DW6" t="n">
-        <v>8.621443703304976e-05</v>
+        <v>6.444467220067737e-14</v>
       </c>
       <c r="DX6" t="n">
-        <v>5.960842827335e-05</v>
+        <v>1.168560284344269e-13</v>
       </c>
       <c r="DY6" t="n">
-        <v>4.101781087229028e-05</v>
+        <v>1.194612036245837e-13</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0001874688168754801</v>
+        <v>1.564060838309123e-13</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0001413464051438496</v>
+        <v>1.89895137375079e-13</v>
       </c>
       <c r="EB6" t="n">
-        <v>4.868777978117578e-05</v>
+        <v>1.47237650132033e-13</v>
       </c>
       <c r="EC6" t="n">
-        <v>7.243394065881148e-06</v>
+        <v>8.75522188927523e-14</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0001385241921525449</v>
+        <v>5.642191154933175e-14</v>
       </c>
       <c r="EE6" t="n">
-        <v>3.885957630700432e-05</v>
+        <v>3.400648225472189e-14</v>
       </c>
       <c r="EF6" t="n">
-        <v>4.497462941799313e-05</v>
+        <v>1.213084672860645e-14</v>
       </c>
       <c r="EG6" t="n">
-        <v>6.742717232555151e-05</v>
+        <v>2.622415529358619e-14</v>
       </c>
       <c r="EH6" t="n">
-        <v>3.085891512455419e-05</v>
+        <v>8.948314230436752e-14</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.000391413748729974</v>
+        <v>1.234253991328968e-13</v>
       </c>
       <c r="EJ6" t="n">
-        <v>6.867761112516746e-05</v>
+        <v>1.316945684448623e-13</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.0002955827221740037</v>
+        <v>7.732497368101443e-14</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0002187731151934713</v>
+        <v>2.331351630572697e-14</v>
       </c>
       <c r="EM6" t="n">
-        <v>6.660939834546298e-05</v>
+        <v>2.221443854062179e-14</v>
       </c>
       <c r="EN6" t="n">
-        <v>6.283822585828602e-05</v>
+        <v>1.123154574986934e-13</v>
       </c>
       <c r="EO6" t="n">
-        <v>8.220404561143368e-05</v>
+        <v>3.782030908610658e-14</v>
       </c>
       <c r="EP6" t="n">
-        <v>5.04605850437656e-05</v>
+        <v>1.394870140615859e-13</v>
       </c>
       <c r="EQ6" t="n">
-        <v>5.64747242606245e-05</v>
+        <v>7.687730321586338e-15</v>
       </c>
       <c r="ER6" t="n">
-        <v>2.15178843063768e-05</v>
+        <v>3.102462812478932e-14</v>
       </c>
       <c r="ES6" t="n">
-        <v>4.434485163073987e-05</v>
+        <v>1.456577100687056e-13</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0001616284425836056</v>
+        <v>3.646463285402607e-14</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0001688182528596371</v>
+        <v>5.342210709718097e-14</v>
       </c>
       <c r="EV6" t="n">
-        <v>1.783134393917862e-05</v>
+        <v>5.283262976413239e-15</v>
       </c>
       <c r="EW6" t="n">
-        <v>8.909760072128847e-05</v>
+        <v>2.440902636805832e-14</v>
       </c>
       <c r="EX6" t="n">
-        <v>1.010816777125001e-05</v>
+        <v>2.662753271185942e-14</v>
       </c>
       <c r="EY6" t="n">
-        <v>3.150062548229471e-05</v>
+        <v>1.835775861836961e-14</v>
       </c>
       <c r="EZ6" t="n">
-        <v>5.115474050398916e-05</v>
+        <v>7.899029466542501e-15</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0001209284891956486</v>
+        <v>1.920513715506639e-14</v>
       </c>
       <c r="FB6" t="n">
-        <v>2.753543958533555e-05</v>
+        <v>5.891215792107329e-14</v>
       </c>
       <c r="FC6" t="n">
-        <v>6.060690793674439e-07</v>
+        <v>8.50635954361377e-14</v>
       </c>
       <c r="FD6" t="n">
-        <v>5.217918442212977e-05</v>
+        <v>3.849382564004994e-14</v>
       </c>
       <c r="FE6" t="n">
-        <v>2.686331208678894e-05</v>
+        <v>3.695498361532337e-14</v>
       </c>
       <c r="FF6" t="n">
-        <v>2.120699718943797e-05</v>
+        <v>7.112249699771367e-14</v>
       </c>
       <c r="FG6" t="n">
-        <v>1.695844730420504e-05</v>
+        <v>2.289586977042429e-13</v>
       </c>
       <c r="FH6" t="n">
-        <v>6.517345900647342e-05</v>
+        <v>8.23920331917069e-14</v>
       </c>
       <c r="FI6" t="n">
-        <v>7.753635145490989e-05</v>
+        <v>7.969426713601985e-14</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0002460043760947883</v>
+        <v>3.619274205422102e-14</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0001329061342403293</v>
+        <v>9.487370402640714e-15</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0001261857978533953</v>
+        <v>1.068547038503807e-13</v>
       </c>
       <c r="FM6" t="n">
-        <v>9.128612146014348e-05</v>
+        <v>3.335108542958619e-14</v>
       </c>
       <c r="FN6" t="n">
-        <v>7.1990471042227e-05</v>
+        <v>2.39941313345815e-13</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.000193394924281165</v>
+        <v>1.366965351676241e-13</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.000146388410939835</v>
+        <v>1.003262685601858e-13</v>
       </c>
       <c r="FQ6" t="n">
-        <v>5.893969137105159e-05</v>
+        <v>1.927962862057972e-13</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0001667734904913232</v>
+        <v>2.812668446674355e-13</v>
       </c>
       <c r="FS6" t="n">
-        <v>3.447035123826936e-05</v>
+        <v>5.279170452025285e-14</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0002787572739180177</v>
+        <v>1.01586206352304e-13</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.000435233669122681</v>
+        <v>1.683268257310182e-14</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0001224031148012727</v>
+        <v>3.248172401621591e-13</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0001604389399290085</v>
+        <v>1.974352891462652e-13</v>
       </c>
       <c r="FX6" t="n">
-        <v>5.523263098439202e-05</v>
+        <v>8.343234550499748e-14</v>
       </c>
       <c r="FY6" t="n">
-        <v>7.606621511513367e-05</v>
+        <v>3.663912841742403e-14</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.0001082213057088666</v>
+        <v>1.268306308230532e-14</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.000105082850495819</v>
+        <v>7.347040456486681e-14</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0001119562948588282</v>
+        <v>2.515354461177233e-14</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0001695762621238828</v>
+        <v>1.653678550431886e-13</v>
       </c>
       <c r="GD6" t="n">
-        <v>9.092404798138887e-05</v>
+        <v>1.001369397558155e-13</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.000329601374687627</v>
+        <v>7.212767184325329e-16</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0002047291491180658</v>
+        <v>1.753866556110026e-13</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0004507010744418949</v>
+        <v>2.769928858221797e-14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.740280475281963e-09</v>
+        <v>1.731235565526401e-18</v>
       </c>
       <c r="B7" t="n">
-        <v>4.137858944375239e-10</v>
+        <v>6.929857369305393e-18</v>
       </c>
       <c r="C7" t="n">
-        <v>1.54514379069326e-09</v>
+        <v>1.660892974095019e-17</v>
       </c>
       <c r="D7" t="n">
-        <v>6.760794701854422e-10</v>
+        <v>2.535793139877863e-17</v>
       </c>
       <c r="E7" t="n">
-        <v>6.661348694869673e-10</v>
+        <v>2.738457022164785e-17</v>
       </c>
       <c r="F7" t="n">
-        <v>1.228560919663835e-09</v>
+        <v>6.388997467571776e-17</v>
       </c>
       <c r="G7" t="n">
-        <v>2.99387670210649e-09</v>
+        <v>3.250526985396555e-18</v>
       </c>
       <c r="H7" t="n">
-        <v>5.65115843009778e-10</v>
+        <v>1.072506334932372e-17</v>
       </c>
       <c r="I7" t="n">
-        <v>4.534874697981195e-10</v>
+        <v>8.200164343549304e-17</v>
       </c>
       <c r="J7" t="n">
-        <v>5.74848502132852e-10</v>
+        <v>4.785690657053106e-18</v>
       </c>
       <c r="K7" t="n">
-        <v>2.05075800785437e-09</v>
+        <v>7.475924703867276e-17</v>
       </c>
       <c r="L7" t="n">
-        <v>1.981810493489888e-09</v>
+        <v>9.678707998584968e-18</v>
       </c>
       <c r="M7" t="n">
-        <v>1.565844343076606e-09</v>
+        <v>4.7801669103586e-17</v>
       </c>
       <c r="N7" t="n">
-        <v>5.674344549788657e-09</v>
+        <v>2.634947445340717e-17</v>
       </c>
       <c r="O7" t="n">
-        <v>2.115223551868439e-10</v>
+        <v>6.655880343894865e-17</v>
       </c>
       <c r="P7" t="n">
-        <v>1.01316932621387e-09</v>
+        <v>1.775729465919021e-17</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.070673632559306e-09</v>
+        <v>4.008392509595599e-17</v>
       </c>
       <c r="R7" t="n">
-        <v>2.096386175765019e-09</v>
+        <v>5.984230862325488e-17</v>
       </c>
       <c r="S7" t="n">
-        <v>1.971577068271557e-10</v>
+        <v>1.908139244420589e-17</v>
       </c>
       <c r="T7" t="n">
-        <v>1.066435273422428e-10</v>
+        <v>4.298177039230076e-17</v>
       </c>
       <c r="U7" t="n">
-        <v>4.596239500109789e-10</v>
+        <v>1.706515459035891e-17</v>
       </c>
       <c r="V7" t="n">
-        <v>6.001067420768891e-10</v>
+        <v>5.362435225402437e-17</v>
       </c>
       <c r="W7" t="n">
-        <v>2.312719460384471e-10</v>
+        <v>7.74149203214416e-17</v>
       </c>
       <c r="X7" t="n">
-        <v>2.426600476113094e-09</v>
+        <v>3.242476532802944e-17</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.162909990526373e-09</v>
+        <v>1.586229005028023e-17</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.331559331331562e-10</v>
+        <v>2.246120279626081e-17</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1090654223066e-10</v>
+        <v>1.940729664246811e-17</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.218238589652316e-11</v>
+        <v>2.309124145342407e-17</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.750795229962023e-10</v>
+        <v>1.320377457492665e-17</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.836045426806265e-09</v>
+        <v>2.496206922739036e-17</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.654069852781049e-09</v>
+        <v>4.642273586140295e-17</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.833622804933384e-10</v>
+        <v>1.817627239279628e-18</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.738495151812572e-10</v>
+        <v>2.437591581044548e-17</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.808099167228022e-10</v>
+        <v>1.385505771176211e-17</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.145418870862613e-09</v>
+        <v>5.070846118543614e-17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.252342451962818e-09</v>
+        <v>1.475288864761391e-17</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.994292839872628e-10</v>
+        <v>2.106140144158427e-17</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.433446972232133e-10</v>
+        <v>1.877640268055146e-17</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.715230540406566e-10</v>
+        <v>1.162974251346684e-17</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.763927444339515e-10</v>
+        <v>4.664646836476384e-17</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.10207140582952e-09</v>
+        <v>2.595582250861564e-17</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.906370640993089e-10</v>
+        <v>5.900041494914637e-18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.635335531550822e-10</v>
+        <v>2.685510514644246e-18</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.486441549493406e-10</v>
+        <v>1.414951167595445e-17</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.448362818567972e-10</v>
+        <v>1.315624312256813e-17</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.062873565884416e-10</v>
+        <v>1.595101675150511e-17</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.841409996179323e-09</v>
+        <v>9.69885216260635e-17</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.932532160495384e-10</v>
+        <v>1.853273016134437e-17</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.309915119764639e-10</v>
+        <v>2.487468752184148e-17</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.404596964935337e-10</v>
+        <v>1.825331020478518e-17</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.714721114571716e-09</v>
+        <v>3.058620669693946e-18</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.197565876637668e-10</v>
+        <v>8.122994678970762e-18</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.194145196758427e-10</v>
+        <v>2.426921778323227e-17</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.843344810126268e-09</v>
+        <v>2.718039723105139e-17</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.123428239324653e-09</v>
+        <v>2.11720476018612e-18</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.852233921795232e-10</v>
+        <v>3.187132194122736e-17</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.157270945739697e-09</v>
+        <v>1.000882089180386e-17</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.120082915306853e-09</v>
+        <v>2.631554185031902e-17</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.745501825884844e-09</v>
+        <v>2.19377397435801e-18</v>
       </c>
       <c r="BH7" t="n">
-        <v>1.277773997720999e-10</v>
+        <v>4.09646110592514e-17</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.929032489300653e-10</v>
+        <v>2.267851803242952e-17</v>
       </c>
       <c r="BJ7" t="n">
-        <v>4.981365320233522e-11</v>
+        <v>3.824503972852406e-17</v>
       </c>
       <c r="BK7" t="n">
-        <v>2.089184159004276e-09</v>
+        <v>2.218685676557902e-17</v>
       </c>
       <c r="BL7" t="n">
-        <v>4.374364204196013e-10</v>
+        <v>3.537827987959903e-17</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.441574054046214e-09</v>
+        <v>2.832831878048308e-17</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.780842554121591e-11</v>
+        <v>1.289773015599122e-17</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.010429766054813e-10</v>
+        <v>8.814456459699764e-18</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.497000188370293e-09</v>
+        <v>3.789588348324297e-17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.3676102472715e-09</v>
+        <v>2.8957267213599e-17</v>
       </c>
       <c r="BR7" t="n">
-        <v>1.706499497267089e-09</v>
+        <v>5.289805789770076e-17</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.758919759315859e-09</v>
+        <v>6.903942214304413e-18</v>
       </c>
       <c r="BT7" t="n">
-        <v>1.355729417618079e-10</v>
+        <v>5.456443143966231e-18</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.731598918754742e-10</v>
+        <v>1.428137584612398e-17</v>
       </c>
       <c r="BV7" t="n">
-        <v>1.347234657167462e-09</v>
+        <v>9.031951194061395e-18</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.536198083826548e-10</v>
+        <v>2.715451309532338e-17</v>
       </c>
       <c r="BX7" t="n">
-        <v>8.865875811281398e-10</v>
+        <v>5.579978432547963e-17</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.992879861134611e-09</v>
+        <v>4.431282311190679e-17</v>
       </c>
       <c r="BZ7" t="n">
-        <v>9.66688284975703e-10</v>
+        <v>4.114525076142073e-17</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.10366826788777e-09</v>
+        <v>9.274054551646477e-18</v>
       </c>
       <c r="CB7" t="n">
-        <v>2.650683006422128e-10</v>
+        <v>3.544000409690774e-17</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.227654755631136e-09</v>
+        <v>4.912792086691677e-17</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.020621309162252e-10</v>
+        <v>1.545513520916938e-17</v>
       </c>
       <c r="CE7" t="n">
-        <v>5.643550071710024e-10</v>
+        <v>4.949419892369709e-18</v>
       </c>
       <c r="CF7" t="n">
-        <v>6.1836549769545e-11</v>
+        <v>2.065019176111069e-18</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.887208610553472e-10</v>
+        <v>1.328544211680401e-17</v>
       </c>
       <c r="CH7" t="n">
-        <v>2.558706024835544e-11</v>
+        <v>9.167895019012034e-19</v>
       </c>
       <c r="CI7" t="n">
-        <v>5.474376507663692e-10</v>
+        <v>1.029557132295149e-17</v>
       </c>
       <c r="CJ7" t="n">
-        <v>6.831257781669819e-10</v>
+        <v>9.362275018336483e-18</v>
       </c>
       <c r="CK7" t="n">
-        <v>4.178702384116662e-10</v>
+        <v>7.721530013293663e-18</v>
       </c>
       <c r="CL7" t="n">
-        <v>4.442717027597354e-10</v>
+        <v>2.129457703881807e-17</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.045655562137426e-09</v>
+        <v>1.152607114011496e-17</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.249144204213849e-09</v>
+        <v>4.050168439251977e-17</v>
       </c>
       <c r="CO7" t="n">
-        <v>5.210092357543772e-10</v>
+        <v>4.871991237541376e-18</v>
       </c>
       <c r="CP7" t="n">
-        <v>6.213197178972507e-10</v>
+        <v>1.846587411551538e-17</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.73726738445157e-09</v>
+        <v>2.6356895917863e-17</v>
       </c>
       <c r="CR7" t="n">
-        <v>5.782029299794544e-10</v>
+        <v>2.008341256847303e-17</v>
       </c>
       <c r="CS7" t="n">
-        <v>1.103263036483781e-09</v>
+        <v>1.296917374549742e-17</v>
       </c>
       <c r="CT7" t="n">
-        <v>1.586887732329956e-09</v>
+        <v>1.91896191011911e-17</v>
       </c>
       <c r="CU7" t="n">
-        <v>9.16665854333587e-10</v>
+        <v>2.539958656006558e-17</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.185349644301393e-11</v>
+        <v>1.80730625862262e-17</v>
       </c>
       <c r="CW7" t="n">
-        <v>5.399705127473453e-10</v>
+        <v>6.945872826735338e-18</v>
       </c>
       <c r="CX7" t="n">
-        <v>5.494051741328221e-11</v>
+        <v>2.344404804674835e-18</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.616925010023863e-10</v>
+        <v>1.676174308731324e-17</v>
       </c>
       <c r="CZ7" t="n">
-        <v>4.339897885508037e-11</v>
+        <v>2.077789190407662e-18</v>
       </c>
       <c r="DA7" t="n">
-        <v>5.122073876151489e-10</v>
+        <v>1.228354772398998e-17</v>
       </c>
       <c r="DB7" t="n">
-        <v>7.813329983008543e-10</v>
+        <v>4.535302258452692e-18</v>
       </c>
       <c r="DC7" t="n">
-        <v>3.980465956843204e-10</v>
+        <v>3.236314781701975e-18</v>
       </c>
       <c r="DD7" t="n">
-        <v>8.675730966967166e-11</v>
+        <v>1.898367925280623e-17</v>
       </c>
       <c r="DE7" t="n">
-        <v>2.705698332050588e-09</v>
+        <v>7.431871215112294e-18</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.649676256183398e-09</v>
+        <v>2.997937790058382e-17</v>
       </c>
       <c r="DG7" t="n">
-        <v>6.771583294096217e-12</v>
+        <v>2.720765944967991e-17</v>
       </c>
       <c r="DH7" t="n">
-        <v>3.395232095471101e-09</v>
+        <v>1.473649889095678e-17</v>
       </c>
       <c r="DI7" t="n">
-        <v>3.911678092549664e-09</v>
+        <v>7.854315662665575e-19</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.658145176719472e-09</v>
+        <v>4.398984878737424e-17</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.896090922632766e-09</v>
+        <v>1.562700348812319e-17</v>
       </c>
       <c r="DL7" t="n">
-        <v>2.541586052728917e-09</v>
+        <v>2.200164937206717e-17</v>
       </c>
       <c r="DM7" t="n">
-        <v>7.176622074389627e-10</v>
+        <v>1.863525754390909e-17</v>
       </c>
       <c r="DN7" t="n">
-        <v>4.409106690861364e-10</v>
+        <v>1.654948192468723e-17</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.964362921797914e-10</v>
+        <v>5.080169436663822e-18</v>
       </c>
       <c r="DP7" t="n">
-        <v>7.825480263790041e-10</v>
+        <v>1.001202787103872e-17</v>
       </c>
       <c r="DQ7" t="n">
-        <v>6.345431957655023e-10</v>
+        <v>4.980830669924369e-17</v>
       </c>
       <c r="DR7" t="n">
-        <v>1.096865931415891e-09</v>
+        <v>2.06601295089899e-17</v>
       </c>
       <c r="DS7" t="n">
-        <v>3.952631277837071e-11</v>
+        <v>3.006502418120756e-17</v>
       </c>
       <c r="DT7" t="n">
-        <v>1.884230327320324e-09</v>
+        <v>2.719705995731066e-17</v>
       </c>
       <c r="DU7" t="n">
-        <v>1.201561961039488e-09</v>
+        <v>9.468630592776101e-18</v>
       </c>
       <c r="DV7" t="n">
-        <v>2.210766847365875e-10</v>
+        <v>7.7189889144519e-18</v>
       </c>
       <c r="DW7" t="n">
-        <v>1.018410009101522e-10</v>
+        <v>2.293594491086214e-17</v>
       </c>
       <c r="DX7" t="n">
-        <v>6.219064707657651e-10</v>
+        <v>1.243202250804019e-17</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.130753765238751e-10</v>
+        <v>2.14166688972309e-17</v>
       </c>
       <c r="DZ7" t="n">
-        <v>1.071222222037704e-09</v>
+        <v>2.272855915076652e-17</v>
       </c>
       <c r="EA7" t="n">
-        <v>3.269880477496656e-10</v>
+        <v>9.133350302270595e-18</v>
       </c>
       <c r="EB7" t="n">
-        <v>3.411661508856412e-10</v>
+        <v>1.775049027147135e-17</v>
       </c>
       <c r="EC7" t="n">
-        <v>7.606698604334383e-10</v>
+        <v>2.944010246331355e-17</v>
       </c>
       <c r="ED7" t="n">
-        <v>1.916515390831819e-09</v>
+        <v>9.517503732088184e-18</v>
       </c>
       <c r="EE7" t="n">
-        <v>6.465492585761012e-10</v>
+        <v>5.449702449154536e-18</v>
       </c>
       <c r="EF7" t="n">
-        <v>3.322640773628649e-10</v>
+        <v>1.280925160895009e-17</v>
       </c>
       <c r="EG7" t="n">
-        <v>1.465628285401976e-09</v>
+        <v>1.052462756073477e-17</v>
       </c>
       <c r="EH7" t="n">
-        <v>4.74101757852452e-10</v>
+        <v>2.103957462676084e-18</v>
       </c>
       <c r="EI7" t="n">
-        <v>1.748504896426084e-09</v>
+        <v>2.675053131904228e-17</v>
       </c>
       <c r="EJ7" t="n">
-        <v>3.018252314745951e-12</v>
+        <v>7.929811609992678e-18</v>
       </c>
       <c r="EK7" t="n">
-        <v>1.077685052308652e-09</v>
+        <v>7.201472463194836e-18</v>
       </c>
       <c r="EL7" t="n">
-        <v>1.67996033750839e-10</v>
+        <v>8.775054538401413e-18</v>
       </c>
       <c r="EM7" t="n">
-        <v>1.43629080850971e-10</v>
+        <v>1.214704058904219e-17</v>
       </c>
       <c r="EN7" t="n">
-        <v>3.472778731250514e-10</v>
+        <v>2.454948311837748e-17</v>
       </c>
       <c r="EO7" t="n">
-        <v>2.21271251321653e-10</v>
+        <v>7.008953620248632e-18</v>
       </c>
       <c r="EP7" t="n">
-        <v>6.961912712988294e-10</v>
+        <v>2.283494615806942e-17</v>
       </c>
       <c r="EQ7" t="n">
-        <v>4.1121418770107e-11</v>
+        <v>1.902369494211909e-17</v>
       </c>
       <c r="ER7" t="n">
-        <v>1.421807560575417e-09</v>
+        <v>2.5079404797281e-18</v>
       </c>
       <c r="ES7" t="n">
-        <v>1.989519105016768e-10</v>
+        <v>6.226616950243942e-18</v>
       </c>
       <c r="ET7" t="n">
-        <v>1.992158105146302e-10</v>
+        <v>2.913484965622433e-17</v>
       </c>
       <c r="EU7" t="n">
-        <v>1.906868274392792e-10</v>
+        <v>2.30717448063862e-17</v>
       </c>
       <c r="EV7" t="n">
-        <v>5.668495672850327e-10</v>
+        <v>1.982544802264224e-17</v>
       </c>
       <c r="EW7" t="n">
-        <v>8.534788431546758e-10</v>
+        <v>1.723996928665464e-17</v>
       </c>
       <c r="EX7" t="n">
-        <v>6.990843320897611e-11</v>
+        <v>2.22138658669401e-17</v>
       </c>
       <c r="EY7" t="n">
-        <v>2.883190353131226e-10</v>
+        <v>9.422617844022226e-18</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1.579839176146791e-10</v>
+        <v>2.04358630605436e-18</v>
       </c>
       <c r="FA7" t="n">
-        <v>2.206543836535957e-10</v>
+        <v>1.067669561736591e-17</v>
       </c>
       <c r="FB7" t="n">
-        <v>7.570835625081429e-11</v>
+        <v>4.253651188986296e-19</v>
       </c>
       <c r="FC7" t="n">
-        <v>9.672299627894176e-10</v>
+        <v>1.128899621347359e-17</v>
       </c>
       <c r="FD7" t="n">
-        <v>8.282134977832811e-10</v>
+        <v>1.355272733377704e-17</v>
       </c>
       <c r="FE7" t="n">
-        <v>6.753815284810116e-10</v>
+        <v>5.816604613707026e-18</v>
       </c>
       <c r="FF7" t="n">
-        <v>1.255765352814464e-10</v>
+        <v>2.286994251542531e-17</v>
       </c>
       <c r="FG7" t="n">
-        <v>4.035088096987494e-10</v>
+        <v>4.324330835837778e-17</v>
       </c>
       <c r="FH7" t="n">
-        <v>5.793076574001077e-10</v>
+        <v>1.510764986872565e-17</v>
       </c>
       <c r="FI7" t="n">
-        <v>5.679012815562601e-12</v>
+        <v>2.080746195661417e-17</v>
       </c>
       <c r="FJ7" t="n">
-        <v>7.097268328593032e-10</v>
+        <v>1.284297576252388e-17</v>
       </c>
       <c r="FK7" t="n">
-        <v>5.423951288108242e-10</v>
+        <v>7.833284595591415e-18</v>
       </c>
       <c r="FL7" t="n">
-        <v>1.69301239694164e-11</v>
+        <v>4.145015946137513e-17</v>
       </c>
       <c r="FM7" t="n">
-        <v>3.14566317438647e-10</v>
+        <v>4.147988502386783e-17</v>
       </c>
       <c r="FN7" t="n">
-        <v>7.499069143435122e-10</v>
+        <v>8.274597860097643e-19</v>
       </c>
       <c r="FO7" t="n">
-        <v>9.738772011047558e-10</v>
+        <v>1.562030663388396e-17</v>
       </c>
       <c r="FP7" t="n">
-        <v>9.930944955272025e-10</v>
+        <v>2.016529021422598e-17</v>
       </c>
       <c r="FQ7" t="n">
-        <v>2.527959397369273e-09</v>
+        <v>4.258169290851091e-17</v>
       </c>
       <c r="FR7" t="n">
-        <v>8.798852757507802e-10</v>
+        <v>1.704236907320553e-17</v>
       </c>
       <c r="FS7" t="n">
-        <v>6.233278337930415e-10</v>
+        <v>4.564857752611457e-17</v>
       </c>
       <c r="FT7" t="n">
-        <v>4.535258835147715e-10</v>
+        <v>8.536277274059406e-18</v>
       </c>
       <c r="FU7" t="n">
-        <v>1.757120227097175e-09</v>
+        <v>3.255481383675441e-18</v>
       </c>
       <c r="FV7" t="n">
-        <v>4.57862803227016e-10</v>
+        <v>3.781804909632418e-17</v>
       </c>
       <c r="FW7" t="n">
-        <v>4.803988318258234e-10</v>
+        <v>3.003087154807647e-17</v>
       </c>
       <c r="FX7" t="n">
-        <v>7.19744153165891e-10</v>
+        <v>3.353208223555213e-17</v>
       </c>
       <c r="FY7" t="n">
-        <v>3.924061076077123e-11</v>
+        <v>1.736274274189222e-17</v>
       </c>
       <c r="FZ7" t="n">
-        <v>1.208389832640933e-09</v>
+        <v>1.569274449448646e-17</v>
       </c>
       <c r="GA7" t="n">
-        <v>1.752002209975956e-09</v>
+        <v>9.222388850586415e-18</v>
       </c>
       <c r="GB7" t="n">
-        <v>4.535459785515172e-10</v>
+        <v>4.728719419544129e-18</v>
       </c>
       <c r="GC7" t="n">
-        <v>2.807600818499623e-09</v>
+        <v>8.340915411347857e-18</v>
       </c>
       <c r="GD7" t="n">
-        <v>1.629172796668854e-09</v>
+        <v>3.546581874946429e-17</v>
       </c>
       <c r="GE7" t="n">
-        <v>1.024511142588835e-09</v>
+        <v>1.227564980350132e-18</v>
       </c>
       <c r="GF7" t="n">
-        <v>1.252596137923945e-09</v>
+        <v>1.720547916383363e-17</v>
       </c>
       <c r="GG7" t="n">
-        <v>5.501323285805881e-10</v>
+        <v>1.766728086493219e-17</v>
       </c>
     </row>
     <row r="8">
@@ -4982,3985 +4982,3985 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0001005186277325265</v>
+        <v>0.002057906240224838</v>
       </c>
       <c r="B9" t="n">
-        <v>0.009741357527673244</v>
+        <v>0.007008420769125223</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0008286318043246865</v>
+        <v>0.000285465968772769</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007720116060227156</v>
+        <v>0.006775597110390663</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003797820070758462</v>
+        <v>0.0006575664156116545</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00291452300734818</v>
+        <v>0.009528506547212601</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0005391634185798466</v>
+        <v>0.00656193308532238</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001965936040505767</v>
+        <v>0.006732043344527483</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002644551917910576</v>
+        <v>0.0006348188617266715</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009607566753402352</v>
+        <v>0.002188196405768394</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00708930566906929</v>
+        <v>0.007723059505224228</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004518194182310253</v>
+        <v>0.001735895406454802</v>
       </c>
       <c r="M9" t="n">
-        <v>0.007436145562678576</v>
+        <v>0.01218067109584808</v>
       </c>
       <c r="N9" t="n">
-        <v>0.006743294652551413</v>
+        <v>0.004649101290851831</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004322621505707502</v>
+        <v>0.01140518113970757</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0003624648088589311</v>
+        <v>0.006674083881080151</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001020315219648182</v>
+        <v>0.0005973531515337527</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003419661661610007</v>
+        <v>0.001950345700606704</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004702437145169824</v>
+        <v>0.00084403355140239</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001398968393914402</v>
+        <v>0.0003922613395843655</v>
       </c>
       <c r="U9" t="n">
-        <v>5.764882371295244e-05</v>
+        <v>0.002089544665068388</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001574868801981211</v>
+        <v>0.001640745205804706</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001877543749287724</v>
+        <v>0.002564150840044022</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0002303100773133337</v>
+        <v>0.003534102579578757</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.00147956854198128</v>
+        <v>0.0004996969946660101</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0003104990464635193</v>
+        <v>0.002281456487253308</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0008757053874433041</v>
+        <v>0.001627087825909257</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0008125712629407644</v>
+        <v>0.002988441847264767</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.002118934411555529</v>
+        <v>0.002768393605947495</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.292221324751154e-05</v>
+        <v>0.002125116530805826</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.001343760406598449</v>
+        <v>0.001226519234478474</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.002827745163813233</v>
+        <v>0.003134527010843158</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001932369079440832</v>
+        <v>0.004419170785695314</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0005733009893447161</v>
+        <v>0.0008749424596317112</v>
       </c>
       <c r="AI9" t="n">
-        <v>9.538000449538231e-05</v>
+        <v>0.005177303217351437</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0003236580523662269</v>
+        <v>0.001874081324785948</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0003252787282690406</v>
+        <v>0.001107998192310333</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0006977001903578639</v>
+        <v>0.002864548936486244</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0001352755789412186</v>
+        <v>0.003082446288317442</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.000200641545234248</v>
+        <v>0.002715307986363769</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.002629641443490982</v>
+        <v>0.0001867704704636708</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001856934744864702</v>
+        <v>0.002488391008228064</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0006562619819305837</v>
+        <v>0.001215822878293693</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0009210227290168405</v>
+        <v>0.002453377936035395</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0009892117232084274</v>
+        <v>0.001495922449976206</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.001378780580125749</v>
+        <v>2.351449802517891e-05</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.007552922237664461</v>
+        <v>0.008248955942690372</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0002330204879399389</v>
+        <v>0.00353146018460393</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.002161007840186357</v>
+        <v>0.004162066150456667</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.000547512318007648</v>
+        <v>0.008477966301143169</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.001695112558081746</v>
+        <v>0.007772901561111212</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.002542705042287707</v>
+        <v>0.0005316846072673798</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.002727876883000135</v>
+        <v>0.0008932701894082129</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.874620496295393e-05</v>
+        <v>5.270971450954676e-05</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.735329326242208e-05</v>
+        <v>0.002665889682248235</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001480417675338686</v>
+        <v>0.001127047697082162</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.002014490775763988</v>
+        <v>0.000687670661136508</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.002305686473846436</v>
+        <v>0.002740781987085938</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.00405640946701169</v>
+        <v>0.004544693045318127</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.00396003108471632</v>
+        <v>0.0003450524527579546</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001711016288027167</v>
+        <v>0.001249530585482717</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.001141774584539235</v>
+        <v>0.004835628438740969</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.002233419101685286</v>
+        <v>0.0005739318439736962</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0009154271683655679</v>
+        <v>0.0008640835876576602</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.002561153145506978</v>
+        <v>0.003094737650826573</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.001141919521614909</v>
+        <v>0.0008577605476602912</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.00121463043615222</v>
+        <v>0.001679571345448494</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.002960932673886418</v>
+        <v>0.0007688989862799644</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.001082730246707797</v>
+        <v>0.000879526836797595</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0007021824712865055</v>
+        <v>0.003379689296707511</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0003263835096731782</v>
+        <v>0.001079893438145518</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001245239400304854</v>
+        <v>0.001743029803037643</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0008866761345416307</v>
+        <v>0.0001670032506808639</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003540646051988006</v>
+        <v>0.004838877823203802</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.00124545709695667</v>
+        <v>0.001992050791159272</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.001842777011916041</v>
+        <v>0.007299632765352726</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0008040196262300014</v>
+        <v>0.00213735643774271</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.000199893896933645</v>
+        <v>0.004378150682896376</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0008463308913633227</v>
+        <v>0.0009888941422104836</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.001717719715088606</v>
+        <v>0.0003481838793959469</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.001214970136061311</v>
+        <v>0.002161832759156823</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0001700897410046309</v>
+        <v>0.0003868812636937946</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001694561564363539</v>
+        <v>0.002581336768344045</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0007317368872463703</v>
+        <v>0.0006979468744248152</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0008998138946481049</v>
+        <v>0.00266643613576889</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0004539814253803343</v>
+        <v>5.758936458732933e-05</v>
       </c>
       <c r="CI9" t="n">
-        <v>8.567160693928599e-05</v>
+        <v>0.001338415429927409</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0001396196894347668</v>
+        <v>0.001288881292566657</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.0002001480461331084</v>
+        <v>0.001392283127643168</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0005419476656243205</v>
+        <v>0.0002604207838885486</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.001913137384690344</v>
+        <v>0.001309838728047907</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0008939721155911684</v>
+        <v>0.003144002752378583</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0003300092066638172</v>
+        <v>0.004962822888046503</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.001727740978822112</v>
+        <v>0.00628958735615015</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0003034005640074611</v>
+        <v>8.114951197057962e-05</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0004769950173795223</v>
+        <v>6.728782318532467e-05</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.001660417881794274</v>
+        <v>0.001879312214441597</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.003031354397535324</v>
+        <v>0.002852215664461255</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0002479410904925317</v>
+        <v>0.0007566986605525017</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0002644962514750659</v>
+        <v>0.0005400351947173476</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.001328532467596233</v>
+        <v>0.002171804197132587</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0009725842392072082</v>
+        <v>4.397728480398655e-05</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.00100136804394424</v>
+        <v>0.003299928968772292</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0006463837926276028</v>
+        <v>0.001011296175420284</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0001136569044319913</v>
+        <v>0.001551642664708197</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0003618176560848951</v>
+        <v>0.001071586273610592</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0002121375437127426</v>
+        <v>0.0011139668058604</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0002330951538169757</v>
+        <v>0.0004731995286419988</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0007782375323586166</v>
+        <v>0.0002922732965089381</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0009374681394547224</v>
+        <v>4.610896576195955e-05</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0006554885185323656</v>
+        <v>0.002457988448441029</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.003318504896014929</v>
+        <v>0.001132723060436547</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001698629348538816</v>
+        <v>0.001306598540395498</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0007471238495782018</v>
+        <v>0.004504930227994919</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0003423893358558416</v>
+        <v>0.0004057697660755366</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0008516650414094329</v>
+        <v>0.008578515611588955</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.000314745120704174</v>
+        <v>0.001850122236646712</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0005659537273459136</v>
+        <v>0.0006866008043289185</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0002514416992198676</v>
+        <v>0.001794651383534074</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.001051825704053044</v>
+        <v>0.0001804752391763031</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0006219791248440742</v>
+        <v>0.0004614178324118257</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0004325101908762008</v>
+        <v>0.001407632720656693</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0002331422438146546</v>
+        <v>0.0002388854627497494</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0014075783547014</v>
+        <v>0.001079856883734465</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0005250056274235249</v>
+        <v>0.003089017234742641</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0005279613542370498</v>
+        <v>0.003821514314040542</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0002355335600441322</v>
+        <v>0.0002562557347118855</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0004063290543854237</v>
+        <v>0.0003217481425963342</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.000735697103664279</v>
+        <v>0.002787907840684056</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0001733993995003402</v>
+        <v>0.002478624228388071</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0001860159827629104</v>
+        <v>0.0009817796526476741</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.002211323473602533</v>
+        <v>0.003032406326383352</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0002994659007526934</v>
+        <v>0.001945215743035078</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.001006499980576336</v>
+        <v>0.004391102585941553</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0001237786782439798</v>
+        <v>0.005306021776050329</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0001285859034396708</v>
+        <v>0.001833807909861207</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.001054587191902101</v>
+        <v>0.0004796739667654037</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0004781408642884344</v>
+        <v>0.002624022774398327</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.00113212363794446</v>
+        <v>0.002466032980009913</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.001538989483378828</v>
+        <v>9.913186659105122e-06</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0001927428384078667</v>
+        <v>0.0004950754228048027</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0006366792949847877</v>
+        <v>0.0005160024738870561</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0002114993694704026</v>
+        <v>0.0003292628680355847</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0007775728590786457</v>
+        <v>0.0004990630550310016</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0005956095992587507</v>
+        <v>0.0006521256873384118</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001557421404868364</v>
+        <v>0.002647632965818048</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0005104595329612494</v>
+        <v>7.069017738103867e-05</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0003485604538582265</v>
+        <v>0.002596486592665315</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0001761389867169783</v>
+        <v>0.000507255201227963</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.002006443683058023</v>
+        <v>0.0002345084794797003</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001597882364876568</v>
+        <v>0.001628217869438231</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0005458603845909238</v>
+        <v>0.0007988843135535717</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0001331974781351164</v>
+        <v>0.004136263392865658</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0001601571420906112</v>
+        <v>0.0005469257012009621</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001265032100491226</v>
+        <v>0.00271163578145206</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0004989643930457532</v>
+        <v>0.0004393956041894853</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0009950657840818167</v>
+        <v>0.003608349710702896</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0009111471008509398</v>
+        <v>3.05859575746581e-05</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0002915627846959978</v>
+        <v>0.001436533755622804</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0004077007761225104</v>
+        <v>0.00190399051643908</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0004272796213626862</v>
+        <v>0.001624306896701455</v>
       </c>
       <c r="FF9" t="n">
-        <v>7.7791053627152e-05</v>
+        <v>0.0004289228818379343</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0001586629368830472</v>
+        <v>0.0001904209493659437</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0002737649192567915</v>
+        <v>0.001578874769620597</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0002808810095302761</v>
+        <v>0.001420049113221467</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.000425330305006355</v>
+        <v>0.002061154460534453</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0007214101497083902</v>
+        <v>0.0008733597351238132</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0005802210653200746</v>
+        <v>0.0006020694272592664</v>
       </c>
       <c r="FM9" t="n">
-        <v>1.540908124297857e-05</v>
+        <v>0.0008363632950931787</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0003700800298247486</v>
+        <v>0.003014410380274057</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0004470516578294337</v>
+        <v>0.00335181737318635</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.001162902684882283</v>
+        <v>0.003622087650001049</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.001004249788820744</v>
+        <v>0.00524830911308527</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0002455179637763649</v>
+        <v>0.004861195106059313</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0009118420421145856</v>
+        <v>0.00471933837980032</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.002222081879153848</v>
+        <v>0.004050246439874172</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0009379833936691284</v>
+        <v>0.002558629494160414</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.001126123825088143</v>
+        <v>0.0004235054948367178</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0005533716175705194</v>
+        <v>0.009748205542564392</v>
       </c>
       <c r="FX9" t="n">
-        <v>6.769259925931692e-05</v>
+        <v>0.0004630093462765217</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.001676237676292658</v>
+        <v>2.756656613200903e-05</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0005976002430543303</v>
+        <v>0.002548789605498314</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0005647296202369034</v>
+        <v>0.001492990646511316</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0009060951415449381</v>
+        <v>0.003754516830667853</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0002068918984150514</v>
+        <v>0.001880645635537803</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.001977812498807907</v>
+        <v>0.003449479816481471</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.002105020917952061</v>
+        <v>0.003328114282339811</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0002131319342879578</v>
+        <v>0.001916462788358331</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0009763670386746526</v>
+        <v>0.001375431893393397</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.04467255622148514</v>
+        <v>0.009842334315180779</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3151176869869232</v>
+        <v>0.0264122448861599</v>
       </c>
       <c r="C10" t="n">
-        <v>0.026175731793046</v>
+        <v>0.002708497922867537</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09909836202859879</v>
+        <v>0.06574403494596481</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0003663729876279831</v>
+        <v>0.01446181535720825</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0480012558400631</v>
+        <v>0.01813472807407379</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02605989389121532</v>
+        <v>0.03746617212891579</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0174800418317318</v>
+        <v>0.03626532852649689</v>
       </c>
       <c r="I10" t="n">
-        <v>3.645196557044983e-05</v>
+        <v>0.02421059273183346</v>
       </c>
       <c r="J10" t="n">
-        <v>0.05231085419654846</v>
+        <v>0.01656276732683182</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1930916011333466</v>
+        <v>0.01517995074391365</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008886849507689476</v>
+        <v>0.00248743942938745</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1329230964183807</v>
+        <v>0.08931927382946014</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06369498372077942</v>
+        <v>0.0467909649014473</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0867852196097374</v>
+        <v>0.007183703128248453</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02585411071777344</v>
+        <v>0.03546502441167831</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.007512988522648811</v>
+        <v>0.008204725570976734</v>
       </c>
       <c r="R10" t="n">
-        <v>0.003964859992265701</v>
+        <v>0.02099640294909477</v>
       </c>
       <c r="S10" t="n">
-        <v>0.007788626477122307</v>
+        <v>0.002274974947795272</v>
       </c>
       <c r="T10" t="n">
-        <v>0.05188189446926117</v>
+        <v>0.009545636363327503</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0241248719394207</v>
+        <v>0.001687530195340514</v>
       </c>
       <c r="V10" t="n">
-        <v>0.03717565909028053</v>
+        <v>0.004803413525223732</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02116987109184265</v>
+        <v>0.003324929857626557</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03043614327907562</v>
+        <v>0.002533045131713152</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.003759677521884441</v>
+        <v>0.006064187735319138</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.009885814040899277</v>
+        <v>0.01708979345858097</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0006861002184450626</v>
+        <v>0.008360493928194046</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.03741830214858055</v>
+        <v>0.003347552381455898</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.045766931027174</v>
+        <v>0.01177297625690699</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.02148037403821945</v>
+        <v>0.005601971875876188</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.004699989221990108</v>
+        <v>0.001850433647632599</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.03021178767085075</v>
+        <v>0.01461322698742151</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003601306118071079</v>
+        <v>0.01822441816329956</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.02316837571561337</v>
+        <v>0.00417916988953948</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01643919944763184</v>
+        <v>0.02092893235385418</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.01231132540851831</v>
+        <v>0.0003103816416114569</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.03720463067293167</v>
+        <v>0.002769459504634142</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01746636629104614</v>
+        <v>0.01505232695490122</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.02290768176317215</v>
+        <v>0.0001044707605615258</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02937626093626022</v>
+        <v>0.006573514081537724</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.03720859065651894</v>
+        <v>0.007360479794442654</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0349901057779789</v>
+        <v>0.006251076236367226</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.01087541691958904</v>
+        <v>0.0164843276143074</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.02553563006222248</v>
+        <v>0.007792276795953512</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.01019906997680664</v>
+        <v>0.005305817350745201</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.01170451752841473</v>
+        <v>0.009040791541337967</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2613078951835632</v>
+        <v>0.01140710525214672</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.02318651415407658</v>
+        <v>0.01187964156270027</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.006151670124381781</v>
+        <v>0.01356529258191586</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.05872098729014397</v>
+        <v>0.05942095816135406</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.02996609918773174</v>
+        <v>0.002071736380457878</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.002953201066702604</v>
+        <v>0.003253816626966</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.02004464715719223</v>
+        <v>0.007205653470009565</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.01029523834586143</v>
+        <v>0.007480580359697342</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.01306270156055689</v>
+        <v>0.01040410436689854</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.06350903958082199</v>
+        <v>0.004732230678200722</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.04439947009086609</v>
+        <v>0.002526991069316864</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.02342292107641697</v>
+        <v>0.0147752221673727</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0654287114739418</v>
+        <v>0.01604280434548855</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.06661695241928101</v>
+        <v>0.004058447200804949</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.01330489106476307</v>
+        <v>0.01182185858488083</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0131788719445467</v>
+        <v>0.03992617130279541</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.001142259221524</v>
+        <v>0.000735376263037324</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.08287476748228073</v>
+        <v>0.0001235487870872021</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.09246161580085754</v>
+        <v>0.00835792813450098</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.01852309331297874</v>
+        <v>0.002431809203699231</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.03144310042262077</v>
+        <v>0.01932888105511665</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.06542312353849411</v>
+        <v>0.01692519150674343</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01342574693262577</v>
+        <v>0.0064879534766078</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0009130947291851044</v>
+        <v>0.008256075903773308</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.02076596207916737</v>
+        <v>0.003788953181356192</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.01613906770944595</v>
+        <v>0.004423418547958136</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.01842227391898632</v>
+        <v>0.000328749418258667</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.127791628241539</v>
+        <v>0.01271038502454758</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.003026327351108193</v>
+        <v>0.005263410974293947</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01433214358985424</v>
+        <v>0.03917370736598969</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01836060918867588</v>
+        <v>0.01820436306297779</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.07713735848665237</v>
+        <v>0.0005908741150051355</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.01590342447161674</v>
+        <v>0.006402415223419666</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0008738772012293339</v>
+        <v>0.000698263174854219</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.003065035212785006</v>
+        <v>0.01030063163489103</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0256572887301445</v>
+        <v>0.006124574691057205</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.05509060621261597</v>
+        <v>0.006428052671253681</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.003971158992499113</v>
+        <v>0.001089462195523083</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0009030551882460713</v>
+        <v>0.02283055335283279</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.01586715690791607</v>
+        <v>0.003031361382454634</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.004944324493408203</v>
+        <v>0.00699886679649353</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.01045369543135166</v>
+        <v>0.008256654255092144</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0003454326651990414</v>
+        <v>0.005850181914865971</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.002017441904172301</v>
+        <v>0.00252443365752697</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.05584266781806946</v>
+        <v>0.0176127627491951</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.06771538406610489</v>
+        <v>0.009815585799515247</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0351012647151947</v>
+        <v>0.01073242351412773</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.07800698280334473</v>
+        <v>0.0441514253616333</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.03624949604272842</v>
+        <v>0.02124487049877644</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.06087411195039749</v>
+        <v>0.007444289978593588</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0205718744546175</v>
+        <v>0.03167834505438805</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.01641936227679253</v>
+        <v>0.006372565869241953</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.004941715858876705</v>
+        <v>0.001842321828007698</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.02661827020347118</v>
+        <v>0.006669067777693272</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.042156882584095</v>
+        <v>0.005237837322056293</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.008078948594629765</v>
+        <v>0.001395608298480511</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.01472387928515673</v>
+        <v>0.02607697620987892</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.01917477138340473</v>
+        <v>0.005310281179845333</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.01037482358515263</v>
+        <v>0.005718134343624115</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.007078221999108791</v>
+        <v>0.006507988087832928</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.000452943699201569</v>
+        <v>0.003702245652675629</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.002361283637583256</v>
+        <v>0.003904670942574739</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.001083070412278175</v>
+        <v>0.01153796538710594</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.03406443074345589</v>
+        <v>0.002328801434487104</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.009883822873234749</v>
+        <v>0.01421668846160173</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01630540378391743</v>
+        <v>0.03930588439106941</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.007773238234221935</v>
+        <v>0.00362105667591095</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.02639710903167725</v>
+        <v>0.004668006673455238</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.01200662273913622</v>
+        <v>0.01286036521196365</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0009894799441099167</v>
+        <v>0.03711657598614693</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0005598990246653557</v>
+        <v>0.009373744949698448</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0555691197514534</v>
+        <v>0.004532958380877972</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.02652864530682564</v>
+        <v>0.0008719179313629866</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.03205879777669907</v>
+        <v>0.008718419820070267</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.003855111543089151</v>
+        <v>0.02039306238293648</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01994404569268227</v>
+        <v>0.001026708167046309</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.02906020358204842</v>
+        <v>0.009314725175499916</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.007048881612718105</v>
+        <v>0.0086326003074646</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.01794473081827164</v>
+        <v>0.00305546959862113</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.007449212484061718</v>
+        <v>0.02642270736396313</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.01292599178850651</v>
+        <v>0.000518777291290462</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.01260372158139944</v>
+        <v>0.004372728988528252</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.03696449100971222</v>
+        <v>0.02087022364139557</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.01950698345899582</v>
+        <v>0.0009233986493200064</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.051786158233881</v>
+        <v>0.0001430546399205923</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.002554812701418996</v>
+        <v>0.008137961849570274</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.002693429822102189</v>
+        <v>0.006227595265954733</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.01146730408072472</v>
+        <v>0.01909670792520046</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.01147558633238077</v>
+        <v>0.001812768168747425</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.03010108321905136</v>
+        <v>0.01466653496026993</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.04302117973566055</v>
+        <v>0.001940083922818303</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.02185460925102234</v>
+        <v>0.004587682895362377</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.00873223040252924</v>
+        <v>0.01921387389302254</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.004594296682626009</v>
+        <v>0.01200493983924389</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.004909224808216095</v>
+        <v>0.006708599161356688</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.002304065972566605</v>
+        <v>0.006340661086142063</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.006778470240533352</v>
+        <v>0.002957617398351431</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.003786234417930245</v>
+        <v>0.0006493219989351928</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.02644497528672218</v>
+        <v>0.004641574807465076</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.03049280494451523</v>
+        <v>0.01090122386813164</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.02653560414910316</v>
+        <v>0.006566063035279512</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0247002374380827</v>
+        <v>0.02517122589051723</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01872206665575504</v>
+        <v>0.002573085017502308</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.05976922810077667</v>
+        <v>0.01084985677152872</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.01668283902108669</v>
+        <v>0.005830733105540276</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0201142393052578</v>
+        <v>0.003711808705702424</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.01571237295866013</v>
+        <v>0.01079660840332508</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0205616969615221</v>
+        <v>0.006959419697523117</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.04464723914861679</v>
+        <v>0.005698470864444971</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.001401151181198657</v>
+        <v>0.0005422802641987801</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.002918836427852511</v>
+        <v>0.03148830309510231</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0004177151713520288</v>
+        <v>0.005545088555663824</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.01497012656182051</v>
+        <v>0.005904624238610268</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.009181284345686436</v>
+        <v>0.004787254612892866</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0002722127828747034</v>
+        <v>0.004368817433714867</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.002409107983112335</v>
+        <v>0.002272718120366335</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.01770677231252193</v>
+        <v>0.008311663754284382</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.008324539288878441</v>
+        <v>3.751396434381604e-05</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.01040673814713955</v>
+        <v>0.001325148856267333</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.01656810753047466</v>
+        <v>0.01330150943249464</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0254649929702282</v>
+        <v>0.0001856801100075245</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.001811354421079159</v>
+        <v>0.001953188329935074</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.01506933197379112</v>
+        <v>0.003323372453451157</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.002389733213931322</v>
+        <v>0.004278224892914295</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.007192697376012802</v>
+        <v>0.01107591763138771</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.01788312941789627</v>
+        <v>0.0174905750900507</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.06196886673569679</v>
+        <v>0.03002011962234974</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.01108863204717636</v>
+        <v>0.009071668609976768</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.06578513979911804</v>
+        <v>0.006191632710397243</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.06431817263364792</v>
+        <v>0.004567502066493034</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.02366132661700249</v>
+        <v>0.02470885030925274</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.01907703094184399</v>
+        <v>0.01420795638114214</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.01489494927227497</v>
+        <v>0.01168191898614168</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.002998445183038712</v>
+        <v>0.009272578172385693</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.03872793540358543</v>
+        <v>0.003929063677787781</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.03749445825815201</v>
+        <v>0.0004269704222679138</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.003408826421946287</v>
+        <v>0.01642157882452011</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.01318141724914312</v>
+        <v>0.02351372875273228</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.03501777350902557</v>
+        <v>0.002548641059547663</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.02559884265065193</v>
+        <v>0.0026286740321666</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.03046827390789986</v>
+        <v>0.0007480401545763016</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.0160890594124794</v>
+        <v>0.001718449639156461</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.003015586175024509</v>
+        <v>0.01253030635416508</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.001804709201678634</v>
+        <v>0.0003894040128216147</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01316954474896193</v>
+        <v>0.002664740895852447</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001602917909622192</v>
+        <v>0.0002343705855309963</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003468082752078772</v>
+        <v>0.002256004838272929</v>
       </c>
       <c r="E11" t="n">
-        <v>0.009332782588899136</v>
+        <v>0.001266542123630643</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001096709165722132</v>
+        <v>0.003284056205302477</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0009999090107157826</v>
+        <v>0.0007220548577606678</v>
       </c>
       <c r="H11" t="n">
-        <v>0.003195840399712324</v>
+        <v>0.002456693910062313</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0008418390061706305</v>
+        <v>0.0004339222214184701</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001807691063731909</v>
+        <v>0.0007389815291389823</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01015213970094919</v>
+        <v>0.003224704880267382</v>
       </c>
       <c r="L11" t="n">
-        <v>6.337012746371329e-05</v>
+        <v>0.0004513456951826811</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0005996876861900091</v>
+        <v>0.001088679535314441</v>
       </c>
       <c r="N11" t="n">
-        <v>0.00565032847225666</v>
+        <v>0.003728882409632206</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003654710599221289</v>
+        <v>0.004081755876541138</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0003324202261865139</v>
+        <v>2.644240157678723e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0004720965807791799</v>
+        <v>0.00105699454434216</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002600046806037426</v>
+        <v>0.0008002661052159965</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0005249622045084834</v>
+        <v>0.0007246496970765293</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001061036949977279</v>
+        <v>0.0002205482014687732</v>
       </c>
       <c r="U11" t="n">
-        <v>0.000848931900691241</v>
+        <v>0.001110712415538728</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001945460098795593</v>
+        <v>0.0007934775203466415</v>
       </c>
       <c r="W11" t="n">
-        <v>0.006690854206681252</v>
+        <v>0.0008373116725124419</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0003607861581258476</v>
+        <v>0.000800424488261342</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.00056781608145684</v>
+        <v>0.0003742518601939082</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.003242685226723552</v>
+        <v>0.0008095250814221799</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0004724125610664487</v>
+        <v>0.0002889794122893363</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0002874319325201213</v>
+        <v>0.00126104464288801</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.001729305600747466</v>
+        <v>0.0004458719631657004</v>
       </c>
       <c r="AD11" t="n">
-        <v>9.445651085115969e-05</v>
+        <v>3.911030944436789e-06</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0006804640870541334</v>
+        <v>9.155122097581625e-05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0004539645742624998</v>
+        <v>0.001358524663373828</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0002381691010668874</v>
+        <v>0.001285626087337732</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0003501700703054667</v>
+        <v>0.001290039625018835</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0002932942879851907</v>
+        <v>0.001767908688634634</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0007880632765591145</v>
+        <v>0.0006026366609148681</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.001608778606168926</v>
+        <v>0.0004100538790225983</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.001813268754631281</v>
+        <v>0.0007486024987883866</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.001172575633972883</v>
+        <v>0.0008112505311146379</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0006270398152992129</v>
+        <v>0.0008001226815395057</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.002344462554901838</v>
+        <v>0.0007971258601173759</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.002575265010818839</v>
+        <v>0.0002219667658209801</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0006928379880264401</v>
+        <v>0.0002162011223845184</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.07331346347928e-05</v>
+        <v>0.0001297042035730556</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0004824597854167223</v>
+        <v>7.72796047385782e-05</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.000365827203495428</v>
+        <v>0.0004283463640604168</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.009578435681760311</v>
+        <v>0.003757764585316181</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0003515510470606387</v>
+        <v>0.0006730934255756438</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.001623506192117929</v>
+        <v>0.0001528819848317653</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.004408668261021376</v>
+        <v>0.001675173058174551</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.003783178981393576</v>
+        <v>0.002207398181781173</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.004631150979548693</v>
+        <v>0.0007361833122558892</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.001183601445518434</v>
+        <v>0.0003449427022133023</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.001068694517016411</v>
+        <v>0.0006006081821396947</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.002276615705341101</v>
+        <v>0.001395369064994156</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.004885307978838682</v>
+        <v>0.0001678810076555237</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.00118972035124898</v>
+        <v>0.0002132584631908685</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0003790336777456105</v>
+        <v>0.002302849199622869</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.0027341996319592</v>
+        <v>0.000630486523732543</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.001022744923830032</v>
+        <v>7.463587098754942e-05</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.002825459465384483</v>
+        <v>0.0003212852170690894</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.0002727134560700506</v>
+        <v>0.002568585798144341</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0003661906812340021</v>
+        <v>0.00109492673072964</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.002868810202926397</v>
+        <v>8.728964894544333e-05</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.004836972802877426</v>
+        <v>0.001507747452706099</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0004739687137771398</v>
+        <v>0.0001737932616379112</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.002710821339860559</v>
+        <v>0.0004227207973599434</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.001813004724681377</v>
+        <v>0.001138558611273766</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.002379100071266294</v>
+        <v>0.001573963789269328</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0006194749148562551</v>
+        <v>0.0004327664501033723</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.002033136552199721</v>
+        <v>0.0002437693619867787</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.001131688011810184</v>
+        <v>0.0009938490111380816</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0005390043370425701</v>
+        <v>0.0001551851455587894</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.006253834813833237</v>
+        <v>0.002190804108977318</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.002412125701084733</v>
+        <v>0.0005586521001532674</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0003265967825427651</v>
+        <v>0.00206120521761477</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.001348461955785751</v>
+        <v>0.0008971670176833868</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.001556665985845029</v>
+        <v>0.00126621569506824</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.001001632306724787</v>
+        <v>0.0001076978223863989</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.001592967193573713</v>
+        <v>0.0006182650104165077</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0005806306144222617</v>
+        <v>0.000755791028495878</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0003861766308546066</v>
+        <v>0.001131550059653819</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.001669558929279447</v>
+        <v>0.0009279596852138638</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.514634070394095e-05</v>
+        <v>0.0004138363292440772</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0003440711589064449</v>
+        <v>0.0003918058064300567</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.001408976735547185</v>
+        <v>0.0001818479504436255</v>
       </c>
       <c r="CI11" t="n">
-        <v>9.235512698069215e-05</v>
+        <v>0.0009442613227292895</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.001136798178777099</v>
+        <v>0.0002909406321123242</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.001376082305796444</v>
+        <v>1.680184504948556e-05</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0003886567137669772</v>
+        <v>1.357541623292491e-05</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.002658767392858863</v>
+        <v>0.0009002388105727732</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.003177395556122065</v>
+        <v>0.001989698503166437</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0001043538213707507</v>
+        <v>0.0009679600480012596</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.002522514900192618</v>
+        <v>0.00087840820197016</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.002504696603864431</v>
+        <v>0.0006239539361558855</v>
       </c>
       <c r="CR11" t="n">
-        <v>6.750784814357758e-05</v>
+        <v>9.391226922161877e-05</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.002260178793221712</v>
+        <v>0.0006392361246980727</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.0009942582109943032</v>
+        <v>0.0005770233692601323</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.001352050574496388</v>
+        <v>0.0003992329875472933</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0001641936542000622</v>
+        <v>0.0009774522623047233</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.001153975259512663</v>
+        <v>0.000657086493447423</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0003730424505192786</v>
+        <v>0.0002050580660579726</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.000829514698125422</v>
+        <v>0.0001785343629308045</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0006769906613044441</v>
+        <v>0.0002998573763761669</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0002046548033831641</v>
+        <v>0.0009734560153447092</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0006709099397994578</v>
+        <v>0.0001362094189971685</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.001254281611181796</v>
+        <v>5.565215906244703e-05</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0005444150883704424</v>
+        <v>1.259348937310278e-05</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.001939560519531369</v>
+        <v>0.000610778690315783</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.000196102395420894</v>
+        <v>0.0008059238898567855</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0008228948572650552</v>
+        <v>0.000528518867213279</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.008175808005034924</v>
+        <v>0.0003144381917081773</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.004189323633909225</v>
+        <v>0.0006629900308325887</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.003765162080526352</v>
+        <v>0.0006526244105771184</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.002325904089957476</v>
+        <v>0.0001955144107341766</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0001931573497131467</v>
+        <v>0.002010735450312495</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.004477566573768854</v>
+        <v>0.001730781979858875</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0007537165656685829</v>
+        <v>0.0007138242362998426</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.000928394147194922</v>
+        <v>0.0002372198068769649</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.001375603722408414</v>
+        <v>9.680475341156125e-05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.001537991221994162</v>
+        <v>0.0008148389752022922</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.002472495194524527</v>
+        <v>0.0007964724209159613</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0007517923368141055</v>
+        <v>7.073531742207706e-05</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.001718366169370711</v>
+        <v>0.0001785711356205866</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0004378504236228764</v>
+        <v>0.001114918850362301</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0020362613722682</v>
+        <v>0.0002711978158913553</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0008687652880325913</v>
+        <v>0.0004566013813018799</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.001057877321727574</v>
+        <v>0.0001394300634274259</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.001151314820162952</v>
+        <v>0.0002433242043480277</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.001222232356667519</v>
+        <v>0.0003350830229464918</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0009399353293702006</v>
+        <v>0.0004025908710900694</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.000405728118494153</v>
+        <v>0.0009827482281252742</v>
       </c>
       <c r="EC11" t="n">
-        <v>9.731290629133582e-05</v>
+        <v>5.50548720639199e-05</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0007506646797992289</v>
+        <v>0.0005212315591052175</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.002556718653067946</v>
+        <v>0.00154059159103781</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0001917746267281473</v>
+        <v>0.0007182251429185271</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.001809202833101153</v>
+        <v>0.0001177038211608306</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0001402734196744859</v>
+        <v>0.0007052627624943852</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0005127431359142065</v>
+        <v>0.0001586204743944108</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.001481248182244599</v>
+        <v>0.0005874466150999069</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.002085964661091566</v>
+        <v>0.0008776974864304066</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0008884700364433229</v>
+        <v>1.4910056052031e-05</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.001327541074715555</v>
+        <v>0.0001574002380948514</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0003947470686398447</v>
+        <v>0.0001280670694541186</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.00142803427297622</v>
+        <v>0.001023872988298535</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.000360078876838088</v>
+        <v>0.000710741151124239</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.001363421091809869</v>
+        <v>0.0003679825167637318</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.00183169892989099</v>
+        <v>0.0001844899961724877</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.000939505232963711</v>
+        <v>0.0009485927876085043</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.001487133675254881</v>
+        <v>0.0006876752013340592</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.001592718181200325</v>
+        <v>0.00029472861206159</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.003138331696391106</v>
+        <v>0.0007832908886484802</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.001059608650393784</v>
+        <v>0.0002713364083319902</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0002674543065950274</v>
+        <v>0.001218644669279456</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0009371739579364657</v>
+        <v>0.0009051184169948101</v>
       </c>
       <c r="EZ11" t="n">
-        <v>4.484155215322971e-05</v>
+        <v>0.0002239366876892745</v>
       </c>
       <c r="FA11" t="n">
-        <v>9.314430644735694e-05</v>
+        <v>0.0003256621421314776</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.001115530612878501</v>
+        <v>8.131624781526625e-06</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0002243522612843663</v>
+        <v>0.0008282104972749949</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.001524106133729219</v>
+        <v>0.0003189420094713569</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.001746392692439258</v>
+        <v>2.629666414577514e-05</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.001069490914233029</v>
+        <v>0.000385687715606764</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0007438465836457908</v>
+        <v>0.0003084121854044497</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.001170520554296672</v>
+        <v>0.0007575122872367501</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0001017330941976979</v>
+        <v>7.116061169654131e-05</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.00301247788593173</v>
+        <v>0.001198335085064173</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0008105417946353555</v>
+        <v>0.0007143996190279722</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0001336813875241205</v>
+        <v>0.0006081313476897776</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.002500085160136223</v>
+        <v>0.0006255245534703135</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.001093167695216835</v>
+        <v>0.001966187264770269</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0003584773803595454</v>
+        <v>0.0007242065039463341</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.002809707541018724</v>
+        <v>0.000557088409550488</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0001738469873089343</v>
+        <v>0.001396493054926395</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.00108787277713418</v>
+        <v>0.0002144078025594354</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.001118892570957541</v>
+        <v>0.0002607236092444509</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.008307590149343014</v>
+        <v>0.001663529663346708</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.002032319782301784</v>
+        <v>0.0002561530563980341</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.001967147225514054</v>
+        <v>0.0002561894943937659</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0007448617834597826</v>
+        <v>0.00261999131180346</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0016028992831707</v>
+        <v>0.0006369413458742201</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.002049610251560807</v>
+        <v>0.001511520007625222</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0008642603643238544</v>
+        <v>0.0005017824587412179</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.001602728967554867</v>
+        <v>0.001026609679684043</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.002041336847469211</v>
+        <v>0.0001781800237949938</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0007983422838151455</v>
+        <v>0.0006332265911623836</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.002858716063201427</v>
+        <v>0.001290623680688441</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.001057668821886182</v>
+        <v>0.0002229152887593955</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.001720804022625089</v>
+        <v>0.0001429524563718587</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.001743484288454056</v>
+        <v>0.001376078929752111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0005421275272965431</v>
+        <v>0.0002006588620133698</v>
       </c>
       <c r="B12" t="n">
-        <v>0.007017014548182487</v>
+        <v>0.00172958173789084</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0005178586579859257</v>
+        <v>0.0003097695298492908</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00473489286378026</v>
+        <v>0.001804166939109564</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001429946045391262</v>
+        <v>0.0002267492964165285</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0009479939471930265</v>
+        <v>0.001295866328291595</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0007322051096707582</v>
+        <v>0.001071536913514137</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0008238213486038148</v>
+        <v>0.0009822577703744173</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0002371341834077612</v>
+        <v>0.0002753687731456012</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0009091034298762679</v>
+        <v>4.460311902221292e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.004688719753175974</v>
+        <v>0.001410457771271467</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0002199600858148187</v>
+        <v>0.0004693072405643761</v>
       </c>
       <c r="M12" t="n">
-        <v>0.004486577585339546</v>
+        <v>0.002480264054611325</v>
       </c>
       <c r="N12" t="n">
-        <v>0.002431206405162811</v>
+        <v>0.00104292412288487</v>
       </c>
       <c r="O12" t="n">
-        <v>0.002221242757514119</v>
+        <v>0.001349624362774193</v>
       </c>
       <c r="P12" t="n">
-        <v>1.240347046405077e-05</v>
+        <v>0.001074110739864409</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0006610424024984241</v>
+        <v>0.0006164080696180463</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0006887895870022476</v>
+        <v>0.0001343164331046864</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0001431135169696063</v>
+        <v>0.0001036879839375615</v>
       </c>
       <c r="T12" t="n">
-        <v>0.001268927939236164</v>
+        <v>1.666986645432189e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0003496657882351428</v>
+        <v>0.0002709688851609826</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0006637480109930038</v>
+        <v>0.000173152657225728</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0001534079492557794</v>
+        <v>0.0004243733128532767</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0009235427714884281</v>
+        <v>0.0004001609340775758</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0009220794891007245</v>
+        <v>0.0002178274444304407</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.00036034663207829</v>
+        <v>0.0002659747842699289</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0004160887619946152</v>
+        <v>0.0001022426295094192</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0005492236232385039</v>
+        <v>0.0002135536924470216</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.001636411994695663</v>
+        <v>3.82453144993633e-05</v>
       </c>
       <c r="AD12" t="n">
-        <v>8.196363341994584e-05</v>
+        <v>0.0003406127216294408</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0005283171194605529</v>
+        <v>0.0004743030003737658</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0006046659545972943</v>
+        <v>0.0005647974321618676</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0002894550270866603</v>
+        <v>0.0007364725461229682</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0007748487405478954</v>
+        <v>0.0003562989877536893</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0003677763743326068</v>
+        <v>0.0004773042746819556</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0001437157916370779</v>
+        <v>0.0002552636724431068</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0003697806969285011</v>
+        <v>9.651628352003172e-05</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0006723279948346317</v>
+        <v>0.0005771787255071104</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0002645216882228851</v>
+        <v>0.0004272867226973176</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0002997212286572903</v>
+        <v>0.0004437011666595936</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0009507997310720384</v>
+        <v>0.0001167145383078605</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0007434516446664929</v>
+        <v>0.0004521986993495375</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0003382059512659907</v>
+        <v>0.0002905801811721176</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.0004496604087762535</v>
+        <v>3.280759847257286e-05</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.000199845468159765</v>
+        <v>0.0001610020408406854</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0006980369798839092</v>
+        <v>0.0004987033316865563</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.00528524536639452</v>
+        <v>0.0007979876245371997</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0001575974165461957</v>
+        <v>0.0006920946761965752</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0002697402087505907</v>
+        <v>0.0003294077469035983</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.000505260075442493</v>
+        <v>0.001617848756723106</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0003043272299692035</v>
+        <v>0.001081977505236864</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.0002385526895523071</v>
+        <v>9.741960093379021e-05</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0004172979097347707</v>
+        <v>3.60476115019992e-05</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.414858317933977e-05</v>
+        <v>0.0002280339685967192</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.0001315209519816563</v>
+        <v>4.772179818246514e-05</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.001067411270923913</v>
+        <v>0.000392592599382624</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.001280451426282525</v>
+        <v>0.0001891317660920322</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.001087871729396284</v>
+        <v>0.0002939965925179422</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.002422482240945101</v>
+        <v>0.0007061967626214027</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0006248062127269804</v>
+        <v>1.730838266666979e-05</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.001230250811204314</v>
+        <v>0.0003498301666695625</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0004865051596425474</v>
+        <v>0.0004248640325386077</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0007104804390110075</v>
+        <v>0.0002120254212059081</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.001073413179256022</v>
+        <v>0.0001797323930077255</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.001303454977460206</v>
+        <v>0.0002153350797016174</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0005040374817326665</v>
+        <v>7.327574712689966e-05</v>
       </c>
       <c r="BO12" t="n">
-        <v>6.12646690569818e-05</v>
+        <v>0.0004484319069888443</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.001126460265368223</v>
+        <v>0.0002491875202395022</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0006512963445857167</v>
+        <v>9.197278995998204e-05</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.001095716375857592</v>
+        <v>9.672278247307986e-05</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.0009854274103417993</v>
+        <v>8.377853373531252e-05</v>
       </c>
       <c r="BT12" t="n">
-        <v>1.710654032649472e-05</v>
+        <v>0.0001205932203447446</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0004249564954079688</v>
+        <v>0.0002235371066490188</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.002738365903496742</v>
+        <v>0.000801681075245142</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0004887334653176367</v>
+        <v>0.0003590792184695601</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0005737544852308929</v>
+        <v>0.0006653832388110459</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0001617732923477888</v>
+        <v>0.0002609556831885129</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.001129106269218028</v>
+        <v>0.00075430708238855</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0001964808034244925</v>
+        <v>0.0003053252294193953</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0001074036190402694</v>
+        <v>1.097648055292666e-05</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.000390538654755801</v>
+        <v>0.0001205345179187134</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0003664852993097156</v>
+        <v>7.908903353381902e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.001244496554136276</v>
+        <v>0.0004096172342542559</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.0003520411846693605</v>
+        <v>8.267124940175563e-05</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0002755771274678409</v>
+        <v>0.0006471275119110942</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0003376070235390216</v>
+        <v>5.856062125531025e-05</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.00028204609407112</v>
+        <v>0.0002523756702430546</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0005182386375963688</v>
+        <v>7.170892058638856e-05</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.634485670365393e-05</v>
+        <v>0.0001898720802273601</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.000266381015535444</v>
+        <v>0.0001055745815392584</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.001106774201616645</v>
+        <v>0.0003859488933812827</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0007644533179700375</v>
+        <v>0.0001484090753365308</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0003824476734735072</v>
+        <v>0.000728797516785562</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.002028700895607471</v>
+        <v>0.0008329748525284231</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0009266281267628074</v>
+        <v>0.0002159811847377568</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.001211118884384632</v>
+        <v>0.000205823453143239</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0008559974376112223</v>
+        <v>0.0005162343150004745</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0009326281142421067</v>
+        <v>1.249928118340904e-05</v>
       </c>
       <c r="CU12" t="n">
-        <v>3.279508382547647e-05</v>
+        <v>0.0003038309223484248</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.0003590763953980058</v>
+        <v>5.889332533115521e-05</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0009409430203959346</v>
+        <v>0.000355716998456046</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0004749826621264219</v>
+        <v>0.000111545727122575</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.000589414790738374</v>
+        <v>0.0006797611713409424</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.000323216081596911</v>
+        <v>0.0002938660327345133</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0003763155546039343</v>
+        <v>0.0002814149775076658</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0005802600062452257</v>
+        <v>3.722187830135226e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>3.992413985542953e-05</v>
+        <v>0.0002108715561917052</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.0001526525593362749</v>
+        <v>0.0001252447254955769</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0004296752449590713</v>
+        <v>0.0004354245320428163</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.001302532735280693</v>
+        <v>0.0003759006503969431</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.00018629505939316</v>
+        <v>0.0001069826830644161</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.001958999549970031</v>
+        <v>0.0006186831160448492</v>
       </c>
       <c r="DI12" t="n">
-        <v>6.1214086599648e-06</v>
+        <v>0.0001148817973444238</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.000635630392935127</v>
+        <v>0.001257891650311649</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0006021236767992377</v>
+        <v>0.0001421383494744077</v>
       </c>
       <c r="DL12" t="n">
-        <v>2.354377647861838e-05</v>
+        <v>0.000854264129884541</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0002982907462865114</v>
+        <v>0.0005395828047767282</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0006599000771529973</v>
+        <v>0.0002200628514401615</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0005025505088269711</v>
+        <v>0.0004722049343399704</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.0006515538552775979</v>
+        <v>6.157948519103229e-06</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0007736815605312586</v>
+        <v>0.0002114090311806649</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.001185436267405748</v>
+        <v>0.000275520549621433</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0004601253313012421</v>
+        <v>0.0002880707033909857</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.0001992234756471589</v>
+        <v>0.0002520770358387381</v>
       </c>
       <c r="DU12" t="n">
-        <v>5.089226760901511e-06</v>
+        <v>0.0002974046219605953</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0003483306791167706</v>
+        <v>0.0006506863282993436</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0001360043243039399</v>
+        <v>5.595300899585709e-05</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0002709910040721297</v>
+        <v>0.0001975222112378106</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0008023789850994945</v>
+        <v>0.0005581030854955316</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0006986662046983838</v>
+        <v>0.0003489591472316533</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.0008207214996218681</v>
+        <v>0.0002022154949372634</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.0003691233578138053</v>
+        <v>0.0003404015151318163</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.0003847303451038897</v>
+        <v>2.998601121362299e-05</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0002671971160452813</v>
+        <v>0.0006348611786961555</v>
       </c>
       <c r="EE12" t="n">
-        <v>3.963214112445712e-07</v>
+        <v>0.0005613447283394635</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.00012873814557679</v>
+        <v>0.0001478857157053426</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0004551108577288687</v>
+        <v>0.000222857590415515</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.000105961284134537</v>
+        <v>0.0002670998219400644</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0003417417756281793</v>
+        <v>0.0006425206083804369</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0009863382438197732</v>
+        <v>0.0001728457427816465</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.000224227987928316</v>
+        <v>0.0001557134091854095</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0009899276774376631</v>
+        <v>0.0001086811971617863</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.000308697548462078</v>
+        <v>5.689363752026111e-05</v>
       </c>
       <c r="EN12" t="n">
-        <v>9.619562479201704e-05</v>
+        <v>9.303657861892134e-06</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.0004431426059454679</v>
+        <v>5.989262717776e-06</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0009528594673611224</v>
+        <v>0.000473446270916611</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0001360107271466404</v>
+        <v>0.0001158029626822099</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0004779224982485175</v>
+        <v>0.0006405768217518926</v>
       </c>
       <c r="ES12" t="n">
-        <v>6.452717934735119e-05</v>
+        <v>0.0001209103356814012</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.001265891711227596</v>
+        <v>6.605943781323731e-06</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0009361488046124578</v>
+        <v>0.0002701235061977059</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.0002836274506989866</v>
+        <v>0.0002342022198718041</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.0001329336228081957</v>
+        <v>0.0005452982732094824</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0001925114629557356</v>
+        <v>7.652688509551808e-05</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0009682538802735507</v>
+        <v>0.0004633358330465853</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.0001968127326108515</v>
+        <v>7.214918150566518e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0005814294563606381</v>
+        <v>0.000711826840415597</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0001581717369845137</v>
+        <v>0.0001015956222545356</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.000540123088285327</v>
+        <v>0.0003285263082943857</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0005887492443434894</v>
+        <v>1.481544131820556e-05</v>
       </c>
       <c r="FE12" t="n">
-        <v>2.031063195317984e-05</v>
+        <v>0.0001966671843547374</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0002585820620879531</v>
+        <v>2.083935578411911e-05</v>
       </c>
       <c r="FG12" t="n">
-        <v>6.193304579937831e-05</v>
+        <v>0.0002092860813718289</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0001193458811030723</v>
+        <v>8.794209134066477e-05</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.0003707317519001663</v>
+        <v>0.0002697680611163378</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.001049736747518182</v>
+        <v>8.959844126366079e-05</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0004695301759056747</v>
+        <v>0.0001785522763384506</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.000354709307430312</v>
+        <v>0.0001281271688640118</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0004748002393171191</v>
+        <v>0.000236358231632039</v>
       </c>
       <c r="FN12" t="n">
-        <v>7.849414396332577e-05</v>
+        <v>0.0001780709717422724</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0001865958474809304</v>
+        <v>0.0003286392893642187</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0002780910290312022</v>
+        <v>0.0003112778067588806</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0004705400206148624</v>
+        <v>0.0001798641169443727</v>
       </c>
       <c r="FR12" t="n">
-        <v>1.644574876991101e-05</v>
+        <v>0.0006537534645758569</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0008809526916593313</v>
+        <v>0.0002189722144976258</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.001218650955706835</v>
+        <v>0.001265014288946986</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0001236658426932991</v>
+        <v>0.0002398667711531743</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.0011855848133564</v>
+        <v>0.0004540805239230394</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0006666326662525535</v>
+        <v>0.0009659238858148456</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.0003752436314243823</v>
+        <v>0.0002488386817276478</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0009561835322529078</v>
+        <v>0.0002188158250646666</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.0003556841693352908</v>
+        <v>5.565441824728623e-05</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0001792156836017966</v>
+        <v>0.0005495110526680946</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.0001106140553019941</v>
+        <v>0.0005735857994295657</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.0009827400790527463</v>
+        <v>0.0003128542739432305</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0006758280796930194</v>
+        <v>0.0007893992587924004</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.001833194866776466</v>
+        <v>0.0005338080227375031</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.0003131489502266049</v>
+        <v>2.412437606835738e-05</v>
       </c>
       <c r="GG12" t="n">
-        <v>4.504876415012404e-06</v>
+        <v>7.706119504291564e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.006925781257450581</v>
+        <v>0.01514316909015179</v>
       </c>
       <c r="B13" t="n">
-        <v>0.08098720759153366</v>
+        <v>0.09239819645881653</v>
       </c>
       <c r="C13" t="n">
-        <v>0.007165289949625731</v>
+        <v>4.14503738284111e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02462103962898254</v>
+        <v>0.07342121005058289</v>
       </c>
       <c r="E13" t="n">
-        <v>0.006516748573631048</v>
+        <v>0.02473127469420433</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07074333727359772</v>
+        <v>0.06936810165643692</v>
       </c>
       <c r="G13" t="n">
-        <v>0.008752630092203617</v>
+        <v>0.03774159774184227</v>
       </c>
       <c r="H13" t="n">
-        <v>0.04407792538404465</v>
+        <v>0.02818864025175571</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01088865753263235</v>
+        <v>0.003979879897087812</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01837500371038914</v>
+        <v>0.004323685541749001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.07998503744602203</v>
+        <v>0.1396404504776001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006755907088518143</v>
+        <v>0.004884951282292604</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01377857476472855</v>
+        <v>0.1082069650292397</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02755704149603844</v>
+        <v>0.0219426304101944</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05437826365232468</v>
+        <v>0.09812428057193756</v>
       </c>
       <c r="P13" t="n">
-        <v>0.004169782157987356</v>
+        <v>0.05340224131941795</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02301324531435966</v>
+        <v>0.01502048969268799</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01912829279899597</v>
+        <v>0.006778694689273834</v>
       </c>
       <c r="S13" t="n">
-        <v>0.000387210282497108</v>
+        <v>0.003179219085723162</v>
       </c>
       <c r="T13" t="n">
-        <v>0.007366723846644163</v>
+        <v>0.02275439351797104</v>
       </c>
       <c r="U13" t="n">
-        <v>0.00213280925527215</v>
+        <v>0.02414315938949585</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01300149224698544</v>
+        <v>0.06914880871772766</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03231401741504669</v>
+        <v>0.119981624186039</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01731517165899277</v>
+        <v>0.04750620946288109</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.002505768090486526</v>
+        <v>0.02613609656691551</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.01473149564117193</v>
+        <v>0.004800430033355951</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.009361728094518185</v>
+        <v>0.02723552659153938</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.001653806306421757</v>
+        <v>0.03775753080844879</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0007949341088533401</v>
+        <v>0.01062360964715481</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.004370787646621466</v>
+        <v>0.0008879731176421046</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.007651226129382849</v>
+        <v>0.01220800634473562</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01378366816788912</v>
+        <v>0.03374743834137917</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01309996377676725</v>
+        <v>0.05678694322705269</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.002682101679965854</v>
+        <v>0.0146821578964591</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.008789367973804474</v>
+        <v>0.03233063220977783</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0004869095573667437</v>
+        <v>0.04080276936292648</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.009764007292687893</v>
+        <v>0.01300163939595222</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.002571789780631661</v>
+        <v>0.01503004785627127</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.005363710224628448</v>
+        <v>0.0009077808354049921</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.008669381961226463</v>
+        <v>0.04737447202205658</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0005929324543103576</v>
+        <v>0.03093750029802322</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.01122918725013733</v>
+        <v>0.02002962864935398</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.001776703633368015</v>
+        <v>0.005968205630779266</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.007772022858262062</v>
+        <v>0.05462297052145004</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.004761345218867064</v>
+        <v>0.02316601388156414</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.007934560999274254</v>
+        <v>0.02919409237802029</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.03562495484948158</v>
+        <v>0.1888843029737473</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.003303254023194313</v>
+        <v>0.02312157675623894</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.01696949452161789</v>
+        <v>0.04028879106044769</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.01196417491883039</v>
+        <v>0.008825498633086681</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.04054255783557892</v>
+        <v>0.04932831600308418</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.02226164750754833</v>
+        <v>0.04723386466503143</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0003435329999774694</v>
+        <v>0.04134353622794151</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.01269564870744944</v>
+        <v>0.02421414852142334</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.002269869204610586</v>
+        <v>0.01837405189871788</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03511319682002068</v>
+        <v>0.02780847996473312</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.01912611350417137</v>
+        <v>0.02418447099626064</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.004374044016003609</v>
+        <v>0.03198790922760963</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.01001670584082603</v>
+        <v>0.006538957357406616</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.01079407706856728</v>
+        <v>0.05048647522926331</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.01091170124709606</v>
+        <v>0.06867886334657669</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.009998885914683342</v>
+        <v>0.01455929595977068</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01356085110455751</v>
+        <v>0.002686499617993832</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.01093824580311775</v>
+        <v>0.02066293731331825</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.01183869317173958</v>
+        <v>0.02719990909099579</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.009609373286366463</v>
+        <v>3.087148070335388e-05</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.01573286950588226</v>
+        <v>0.02136300131678581</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.004018702544271946</v>
+        <v>0.004700759425759315</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.001077070599421859</v>
+        <v>0.00787358358502388</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.001998314633965492</v>
+        <v>0.07430377602577209</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.01051904447376728</v>
+        <v>0.01965032890439034</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.003815381787717342</v>
+        <v>0.01736475341022015</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.00247138156555593</v>
+        <v>0.01528104115277529</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.02805331349372864</v>
+        <v>0.09164992719888687</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.003421864472329617</v>
+        <v>0.01455746777355671</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.007282382808625698</v>
+        <v>0.0795697420835495</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.001355088781565428</v>
+        <v>0.1114795878529549</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.02048272080719471</v>
+        <v>0.08176553249359131</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.007152884267270565</v>
+        <v>0.01014612428843975</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.002510116901248693</v>
+        <v>0.01754351519048214</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.005886434577405453</v>
+        <v>0.04072482883930206</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.001896846573799849</v>
+        <v>0.01138769183307886</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.01250018179416656</v>
+        <v>0.03362714499235153</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.006901361048221588</v>
+        <v>0.0001635344233363867</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0005996379186399281</v>
+        <v>0.01410382986068726</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.001111578196287155</v>
+        <v>0.006905458867549896</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.01181646436452866</v>
+        <v>0.03237626329064369</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.005101527087390423</v>
+        <v>0.02358517795801163</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.007669703103601933</v>
+        <v>0.01005510613322258</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.006560755427926779</v>
+        <v>0.003376633394509554</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.008621521294116974</v>
+        <v>0.04869511350989342</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.01061274204403162</v>
+        <v>0.1075246036052704</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.001695038052275777</v>
+        <v>0.001907636411488056</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.01806509122252464</v>
+        <v>0.01131573505699635</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.003506039502099156</v>
+        <v>0.08228696137666702</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.005554220639169216</v>
+        <v>0.09990135580301285</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0188422966748476</v>
+        <v>0.03123182058334351</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01319700852036476</v>
+        <v>0.05402190238237381</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.004448237828910351</v>
+        <v>0.04661805182695389</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001975310035049915</v>
+        <v>0.01650012843310833</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01150212623178959</v>
+        <v>0.02928479388356209</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.006165921688079834</v>
+        <v>0.001135927625000477</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.00177165144123137</v>
+        <v>0.008020472712814808</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.001516016898676753</v>
+        <v>0.003032668959349394</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.01096990797668695</v>
+        <v>0.01966239511966705</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.004469369072467089</v>
+        <v>0.0145238833501935</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.009479767642915249</v>
+        <v>0.01153386011719704</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.004215761553496122</v>
+        <v>9.416369721293449e-05</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.008333214558660984</v>
+        <v>0.001736240810714662</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.003901165444403887</v>
+        <v>0.02605482190847397</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.0002622707397677004</v>
+        <v>0.03041460178792477</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.03865503519773483</v>
+        <v>6.174482405185699e-05</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01446626707911491</v>
+        <v>0.00426902249455452</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.03210204467177391</v>
+        <v>0.03440399467945099</v>
       </c>
       <c r="DK13" t="n">
-        <v>8.929637260735035e-05</v>
+        <v>0.0321551077067852</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.01232302375137806</v>
+        <v>0.001925438642501831</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.01851769722998142</v>
+        <v>0.06539100408554077</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.002936348784714937</v>
+        <v>0.01692100986838341</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.002144961385056376</v>
+        <v>0.008493078872561455</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.01314032357186079</v>
+        <v>0.0003360434202477336</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.005968923680484295</v>
+        <v>0.0780998021364212</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01216916367411613</v>
+        <v>0.02474400959908962</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.007089540362358093</v>
+        <v>0.0217271763831377</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.003452482167631388</v>
+        <v>0.01348678860813379</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.001265175873413682</v>
+        <v>0.04841407388448715</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0004762235912494361</v>
+        <v>0.00317534152418375</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.002268764190375805</v>
+        <v>0.02277281507849693</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.002771914703771472</v>
+        <v>0.02071809954941273</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.00115136057138443</v>
+        <v>0.01966327428817749</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.007336419075727463</v>
+        <v>0.05137503519654274</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.006070573348551989</v>
+        <v>0.02438936196267605</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01780388318002224</v>
+        <v>0.04327193647623062</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.003069023136049509</v>
+        <v>0.008960878476500511</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.007619400043040514</v>
+        <v>0.03596232831478119</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.01840002276003361</v>
+        <v>0.0009813886135816574</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.003543095663189888</v>
+        <v>0.01767919212579727</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0176849253475666</v>
+        <v>0.01142803020775318</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.005878349300473928</v>
+        <v>0.003298390656709671</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.009106210432946682</v>
+        <v>0.03895245492458344</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.004282329697161913</v>
+        <v>0.02450809627771378</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0008838560897856951</v>
+        <v>0.0009126373333856463</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.001893039792776108</v>
+        <v>0.001821706537157297</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.004741192795336246</v>
+        <v>0.001574758556671441</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.00373583217151463</v>
+        <v>0.01576140150427818</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.00262839812785387</v>
+        <v>0.004255569539964199</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.008780489675700665</v>
+        <v>0.004281307104974985</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0008498369716107845</v>
+        <v>0.007704886142164469</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.004580208100378513</v>
+        <v>0.007047282531857491</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.003705810755491257</v>
+        <v>0.02232286334037781</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01117480173707008</v>
+        <v>0.03136545047163963</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.01186141557991505</v>
+        <v>0.0150906965136528</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.02983933314681053</v>
+        <v>0.0220954455435276</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.005837834905833006</v>
+        <v>0.007216089405119419</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.001374539569951594</v>
+        <v>0.015974011272192</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.009092720225453377</v>
+        <v>0.03912299126386642</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.003112006932497025</v>
+        <v>0.0005922680720686913</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.001394810620695353</v>
+        <v>0.001676645129919052</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.002229179255664349</v>
+        <v>0.0005702553316950798</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.009718034416437149</v>
+        <v>0.02928252518177032</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.009092728607356548</v>
+        <v>0.02690602838993073</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.009471409022808075</v>
+        <v>0.01055308524519205</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.006119697820395231</v>
+        <v>0.005616507492959499</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.008849376812577248</v>
+        <v>0.01362236589193344</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.004373165313154459</v>
+        <v>0.04321495816111565</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.00337172020226717</v>
+        <v>0.01315488293766975</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.01549582369625568</v>
+        <v>0.02712789922952652</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.002337507205083966</v>
+        <v>0.005252995528280735</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.005348636768758297</v>
+        <v>0.03139922767877579</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.008649356663227081</v>
+        <v>0.01990457996726036</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.004580747801810503</v>
+        <v>0.01227531395852566</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.001871479791589081</v>
+        <v>0.001144037581980228</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.005355184897780418</v>
+        <v>0.0231437049806118</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.015502555295825</v>
+        <v>0.1174053847789764</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.01012058556079865</v>
+        <v>0.000860447995364666</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.01298594195395708</v>
+        <v>0.05575604364275932</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.02900824882090092</v>
+        <v>0.09293271601200104</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01693073660135269</v>
+        <v>0.01708964817225933</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.01562159229069948</v>
+        <v>0.06026636064052582</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.01080255769193172</v>
+        <v>0.00724386190995574</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01162608712911606</v>
+        <v>0.04509789124131203</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.01233600918203592</v>
+        <v>0.001117573585361242</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01243624184280634</v>
+        <v>0.001600863644853234</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.003706611227244139</v>
+        <v>0.01982779614627361</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.01250858791172504</v>
+        <v>0.007698807865381241</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.007360548246651888</v>
+        <v>0.06028170138597488</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.002999479882419109</v>
+        <v>0.02521398104727268</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.01958036422729492</v>
+        <v>0.01387031283229589</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.01202917657792568</v>
+        <v>0.001218496588990092</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.001007437240332365</v>
+        <v>0.02115693874657154</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3.804812513408251e-05</v>
+        <v>0.02175251953303814</v>
       </c>
       <c r="B14" t="n">
-        <v>0.00198183604516089</v>
+        <v>0.06542608886957169</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0002014678902924061</v>
+        <v>0.003851938992738724</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0009693618630990386</v>
+        <v>0.07334044575691223</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0004883497022092342</v>
+        <v>0.01267413701862097</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0002460324321873486</v>
+        <v>0.04501417279243469</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001635604712646455</v>
+        <v>0.03085502982139587</v>
       </c>
       <c r="H14" t="n">
-        <v>6.776020745746791e-05</v>
+        <v>0.02941368520259857</v>
       </c>
       <c r="I14" t="n">
-        <v>0.000104063939943444</v>
+        <v>0.01335789635777473</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001155617646872997</v>
+        <v>0.006984846666455269</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001458251615986228</v>
+        <v>0.0765426978468895</v>
       </c>
       <c r="L14" t="n">
-        <v>2.406240673735738e-05</v>
+        <v>0.01416376885026693</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0008158964919857681</v>
+        <v>0.09481455385684967</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0005593072273768485</v>
+        <v>0.04177563637495041</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0002399586519459262</v>
+        <v>0.04906551539897919</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001382851478410885</v>
+        <v>0.01928230002522469</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0003493349358905107</v>
+        <v>0.001236174255609512</v>
       </c>
       <c r="R14" t="n">
-        <v>1.213783070852514e-05</v>
+        <v>0.006786033976823092</v>
       </c>
       <c r="S14" t="n">
-        <v>8.244887430919334e-05</v>
+        <v>0.007399505469948053</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0003123147180303931</v>
+        <v>0.006874993443489075</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0001184396896860562</v>
+        <v>0.008038235828280449</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0002486087614670396</v>
+        <v>0.006710061337798834</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0001707628543954343</v>
+        <v>0.01461662724614143</v>
       </c>
       <c r="X14" t="n">
-        <v>0.000194069289136678</v>
+        <v>0.01425302308052778</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0001402657508151606</v>
+        <v>0.01557862292975187</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0001990044984268025</v>
+        <v>0.02113070525228977</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0001063579693436623</v>
+        <v>0.00242282566614449</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.79612421663478e-05</v>
+        <v>0.005861230660229921</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.713775655953214e-05</v>
+        <v>0.002784451469779015</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0001139083105954342</v>
+        <v>0.005414352752268314</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.873818448279053e-05</v>
+        <v>0.03105275705456734</v>
       </c>
       <c r="AF14" t="n">
-        <v>5.347428668756038e-07</v>
+        <v>0.01553560607135296</v>
       </c>
       <c r="AG14" t="n">
-        <v>9.238165512215346e-05</v>
+        <v>0.0287761352956295</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.754697223077528e-05</v>
+        <v>0.001026028534397483</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0001779014419298619</v>
+        <v>0.04177286475896835</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.255081951967441e-05</v>
+        <v>0.006055482663214207</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0002435202623018995</v>
+        <v>0.001822059508413076</v>
       </c>
       <c r="AL14" t="n">
-        <v>9.870497160591185e-05</v>
+        <v>0.01207585539668798</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.331756902800407e-05</v>
+        <v>0.01184701267629862</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0001756673154886812</v>
+        <v>0.02495912276208401</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0002231289690826088</v>
+        <v>0.0001523972023278475</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0002531261707190424</v>
+        <v>0.009647627361118793</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.103081927401945e-05</v>
+        <v>0.00022161565721035</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0001932065497385338</v>
+        <v>0.0106161730363965</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.123812924372032e-05</v>
+        <v>0.004131278954446316</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.084821244352497e-05</v>
+        <v>0.007647157646715641</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.00123986741527915</v>
+        <v>0.05655303969979286</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.555492028477602e-05</v>
+        <v>0.01910753920674324</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0001393005804857239</v>
+        <v>0.01795043423771858</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.061171951732831e-05</v>
+        <v>0.05325670167803764</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.310523243271746e-05</v>
+        <v>0.03178969398140907</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0001317371934419498</v>
+        <v>0.0005972083890810609</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0002639052690938115</v>
+        <v>0.004952414892613888</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.933886753453407e-05</v>
+        <v>0.01055756770074368</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.261400757357478e-05</v>
+        <v>0.004424282349646091</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0003024258476216346</v>
+        <v>0.01867532730102539</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0004181313852313906</v>
+        <v>0.005768146365880966</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0002816747000906616</v>
+        <v>0.01936918497085571</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0006704672705382109</v>
+        <v>0.04379791393876076</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0001055701359291561</v>
+        <v>0.002742734272032976</v>
       </c>
       <c r="BI14" t="n">
-        <v>6.246074190130457e-05</v>
+        <v>0.0007135737687349319</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0002925878798123449</v>
+        <v>0.03177540749311447</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.255752017139457e-05</v>
+        <v>0.0005039270035922527</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0001857781899161637</v>
+        <v>0.009366440586745739</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0004065970424562693</v>
+        <v>0.02549001015722752</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0001524675171822309</v>
+        <v>0.0001258370466530323</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.586479604360647e-05</v>
+        <v>0.02179798856377602</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0002750490966718644</v>
+        <v>0.02725112065672874</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0001964390685316175</v>
+        <v>0.01135531812906265</v>
       </c>
       <c r="BR14" t="n">
-        <v>3.877039125654846e-05</v>
+        <v>0.007204643450677395</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0001047718469635583</v>
+        <v>0.01254323404282331</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.573504651896656e-05</v>
+        <v>0.007506088819354773</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0001112917379941791</v>
+        <v>0.0003314791829325259</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0006875465624034405</v>
+        <v>0.03308698907494545</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0002013600169448182</v>
+        <v>0.008646597154438496</v>
       </c>
       <c r="BX14" t="n">
-        <v>8.358381455764174e-05</v>
+        <v>0.02455721236765385</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.260685712622944e-05</v>
+        <v>3.747176378965378e-05</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0002494719228707254</v>
+        <v>0.02225072681903839</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0001651030324865133</v>
+        <v>0.01974137686192989</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.869322583544999e-05</v>
+        <v>0.00278633669950068</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.129728116211481e-05</v>
+        <v>0.00204312545247376</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.671413312782533e-05</v>
+        <v>0.006084322463721037</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0003323848068248481</v>
+        <v>0.01803917065262794</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0001072680315701291</v>
+        <v>0.0008777568000368774</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0001325923803960904</v>
+        <v>0.022056944668293</v>
       </c>
       <c r="CH14" t="n">
-        <v>8.064731810009107e-05</v>
+        <v>0.007400407455861568</v>
       </c>
       <c r="CI14" t="n">
-        <v>6.27771150902845e-05</v>
+        <v>0.00880518089979887</v>
       </c>
       <c r="CJ14" t="n">
-        <v>7.887656101956964e-05</v>
+        <v>0.003297366667538881</v>
       </c>
       <c r="CK14" t="n">
-        <v>5.444659473141655e-05</v>
+        <v>0.004449717700481415</v>
       </c>
       <c r="CL14" t="n">
-        <v>7.241642742883414e-05</v>
+        <v>0.002955683507025242</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0004208874306641519</v>
+        <v>0.02707869000732899</v>
       </c>
       <c r="CN14" t="n">
-        <v>7.951238512760028e-05</v>
+        <v>0.03808166086673737</v>
       </c>
       <c r="CO14" t="n">
-        <v>9.79187898337841e-05</v>
+        <v>0.02440261654555798</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0002193737600464374</v>
+        <v>0.02916039898991585</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0002083877770928666</v>
+        <v>0.01805366948246956</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0004521396185737103</v>
+        <v>0.002567187882959843</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0002021545224124566</v>
+        <v>0.01697650365531445</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0001754081749822944</v>
+        <v>0.01530573517084122</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.000185377401066944</v>
+        <v>0.002039991319179535</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.086352222046116e-05</v>
+        <v>0.003928143065422773</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0003029675863217562</v>
+        <v>0.01656817644834518</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.000141991040436551</v>
+        <v>0.001788811758160591</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0001964170078281313</v>
+        <v>0.0266830176115036</v>
       </c>
       <c r="CZ14" t="n">
-        <v>7.62797353672795e-05</v>
+        <v>0.01134197320789099</v>
       </c>
       <c r="DA14" t="n">
-        <v>5.125319876242429e-05</v>
+        <v>0.008723806589841843</v>
       </c>
       <c r="DB14" t="n">
-        <v>8.875023195287213e-05</v>
+        <v>0.004337108694016933</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0001029633422149345</v>
+        <v>0.005715378560125828</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.572517354972661e-05</v>
+        <v>0.004246328491717577</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0001241186255356297</v>
+        <v>0.009526379406452179</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0005808182177133858</v>
+        <v>0.004683211445808411</v>
       </c>
       <c r="DG14" t="n">
-        <v>7.952710438985378e-05</v>
+        <v>0.01506637036800385</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0005443461122922599</v>
+        <v>0.02338891476392746</v>
       </c>
       <c r="DI14" t="n">
-        <v>1.591702675796114e-05</v>
+        <v>0.008566521108150482</v>
       </c>
       <c r="DJ14" t="n">
-        <v>6.297121581155807e-05</v>
+        <v>0.01737026125192642</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.0001263825979549438</v>
+        <v>0.0002075864467769861</v>
       </c>
       <c r="DL14" t="n">
-        <v>7.866400846978649e-05</v>
+        <v>0.03963639959692955</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.000103749698610045</v>
+        <v>0.01046944409608841</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0002003439876716584</v>
+        <v>0.00432599987834692</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.000141267038998194</v>
+        <v>0.02357185631990433</v>
       </c>
       <c r="DP14" t="n">
-        <v>3.767801536014304e-05</v>
+        <v>0.003771752817556262</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0001092303864425048</v>
+        <v>0.01568345539271832</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.0001026999379973859</v>
+        <v>0.009737065061926842</v>
       </c>
       <c r="DS14" t="n">
-        <v>7.979549991432577e-05</v>
+        <v>0.01161592453718185</v>
       </c>
       <c r="DT14" t="n">
-        <v>8.68059869389981e-05</v>
+        <v>0.02264194190502167</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0001089747966034338</v>
+        <v>0.02170423418283463</v>
       </c>
       <c r="DV14" t="n">
-        <v>5.122553920955397e-05</v>
+        <v>0.0123048322275281</v>
       </c>
       <c r="DW14" t="n">
-        <v>2.716815833991859e-05</v>
+        <v>0.006206153891980648</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0001541696692584082</v>
+        <v>0.001102567068301141</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0001375853316858411</v>
+        <v>0.01000681053847075</v>
       </c>
       <c r="DZ14" t="n">
-        <v>6.794530781917274e-05</v>
+        <v>0.008427941240370274</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.000253767502726987</v>
+        <v>0.02577933482825756</v>
       </c>
       <c r="EB14" t="n">
-        <v>5.384771793615073e-05</v>
+        <v>0.00427767401561141</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0001417532039340585</v>
+        <v>0.008140861056745052</v>
       </c>
       <c r="ED14" t="n">
-        <v>5.92381002206821e-05</v>
+        <v>0.0463503785431385</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0001707951887510717</v>
+        <v>0.02180789038538933</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0002152936067432165</v>
+        <v>0.003822190687060356</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0002969768247567117</v>
+        <v>0.002201693132519722</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.0001857862225733697</v>
+        <v>0.007100878283381462</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0001342034229310229</v>
+        <v>0.0106433629989624</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0001030813145916909</v>
+        <v>0.01367542706429958</v>
       </c>
       <c r="EK14" t="n">
-        <v>4.479335984797217e-05</v>
+        <v>0.007893823087215424</v>
       </c>
       <c r="EL14" t="n">
-        <v>8.704634092282504e-05</v>
+        <v>0.00584912346675992</v>
       </c>
       <c r="EM14" t="n">
-        <v>4.972238093614578e-05</v>
+        <v>0.002746947109699249</v>
       </c>
       <c r="EN14" t="n">
-        <v>2.234325438621454e-05</v>
+        <v>0.002021140651777387</v>
       </c>
       <c r="EO14" t="n">
-        <v>5.080363916931674e-05</v>
+        <v>0.003821970894932747</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0001782457402441651</v>
+        <v>0.01299481280148029</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0001297951239394024</v>
+        <v>0.003399382811039686</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0001343434996670112</v>
+        <v>0.01294204778969288</v>
       </c>
       <c r="ES14" t="n">
-        <v>9.874484385363758e-05</v>
+        <v>0.02033743634819984</v>
       </c>
       <c r="ET14" t="n">
-        <v>5.705261719413102e-05</v>
+        <v>0.001111678779125214</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.000202418930712156</v>
+        <v>0.01144582312554121</v>
       </c>
       <c r="EV14" t="n">
-        <v>1.304166653426364e-05</v>
+        <v>0.003655776381492615</v>
       </c>
       <c r="EW14" t="n">
-        <v>4.998685108148493e-05</v>
+        <v>0.01767510920763016</v>
       </c>
       <c r="EX14" t="n">
-        <v>5.872438850929029e-05</v>
+        <v>0.003910238388925791</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0003104340576101094</v>
+        <v>0.01957045868039131</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0001133908954216167</v>
+        <v>8.648354560136795e-05</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0001606024452485144</v>
+        <v>0.02780593186616898</v>
       </c>
       <c r="FB14" t="n">
-        <v>3.18317070195917e-05</v>
+        <v>0.005550073459744453</v>
       </c>
       <c r="FC14" t="n">
-        <v>6.93027104716748e-05</v>
+        <v>0.00999276340007782</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0001035949244396761</v>
+        <v>0.001791895600035787</v>
       </c>
       <c r="FE14" t="n">
-        <v>7.479853229597211e-05</v>
+        <v>0.007253441959619522</v>
       </c>
       <c r="FF14" t="n">
-        <v>9.216376201948151e-05</v>
+        <v>0.0006148458924144506</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0001154865021817386</v>
+        <v>0.006718546152114868</v>
       </c>
       <c r="FH14" t="n">
-        <v>4.469434861675836e-05</v>
+        <v>0.004252732265740633</v>
       </c>
       <c r="FI14" t="n">
-        <v>5.667484583682381e-05</v>
+        <v>0.01352997217327356</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0002081558632198721</v>
+        <v>0.02096062339842319</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0002223039482487366</v>
+        <v>8.768439874984324e-05</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0001805889623938128</v>
+        <v>0.01056998688727617</v>
       </c>
       <c r="FM14" t="n">
-        <v>5.976057218504138e-05</v>
+        <v>0.008883346803486347</v>
       </c>
       <c r="FN14" t="n">
-        <v>5.218218939262442e-05</v>
+        <v>0.008715415373444557</v>
       </c>
       <c r="FO14" t="n">
-        <v>3.618084156187251e-05</v>
+        <v>0.02048460207879543</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0001748322101775557</v>
+        <v>0.02726668491959572</v>
       </c>
       <c r="FQ14" t="n">
-        <v>1.692720616119914e-05</v>
+        <v>0.00660257413983345</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.0004184952122159302</v>
+        <v>0.0299316979944706</v>
       </c>
       <c r="FS14" t="n">
-        <v>4.149080996285193e-05</v>
+        <v>0.0006122244521975517</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0002516984823159873</v>
+        <v>0.01445683464407921</v>
       </c>
       <c r="FU14" t="n">
-        <v>7.578057557111606e-05</v>
+        <v>0.005391991231590509</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0001099748624255881</v>
+        <v>0.02143167145550251</v>
       </c>
       <c r="FW14" t="n">
-        <v>8.773934678174555e-05</v>
+        <v>0.01758958585560322</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0002296513266628608</v>
+        <v>0.004587672650814056</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0002346368128200993</v>
+        <v>0.003383609000593424</v>
       </c>
       <c r="FZ14" t="n">
-        <v>9.538250196783338e-06</v>
+        <v>0.005145504139363766</v>
       </c>
       <c r="GA14" t="n">
-        <v>2.43465110543184e-05</v>
+        <v>0.01246329490095377</v>
       </c>
       <c r="GB14" t="n">
-        <v>3.892721724696457e-05</v>
+        <v>0.01164628565311432</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0001142476903623901</v>
+        <v>0.0005842612590640783</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0001815770956454799</v>
+        <v>0.01729179546236992</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0003141624620184302</v>
+        <v>0.03320364654064178</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0001035308232530951</v>
+        <v>0.0005003443220630288</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0001808154338505119</v>
+        <v>0.003695250023156404</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.004299047403037548</v>
+        <v>0.01696557365357876</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1323132812976837</v>
+        <v>0.2236759960651398</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02556011267006397</v>
+        <v>0.05945539474487305</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08938220143318176</v>
+        <v>0.4598589539527893</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05522022768855095</v>
+        <v>0.04047000408172607</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01822698302567005</v>
+        <v>0.1549058258533478</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03506369516253471</v>
+        <v>0.2217611074447632</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01760620065033436</v>
+        <v>0.2353326678276062</v>
       </c>
       <c r="I15" t="n">
-        <v>0.003098417073488235</v>
+        <v>0.04505127668380737</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01595834083855152</v>
+        <v>0.04478293284773827</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09919295459985733</v>
+        <v>0.1710361540317535</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01294318772852421</v>
+        <v>0.04169447720050812</v>
       </c>
       <c r="M15" t="n">
-        <v>0.08744070678949356</v>
+        <v>0.6250255703926086</v>
       </c>
       <c r="N15" t="n">
-        <v>0.06548935174942017</v>
+        <v>0.05063359439373016</v>
       </c>
       <c r="O15" t="n">
-        <v>0.04562109708786011</v>
+        <v>0.152511864900589</v>
       </c>
       <c r="P15" t="n">
-        <v>0.02802520431578159</v>
+        <v>0.2416406869888306</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.007696942426264286</v>
+        <v>0.07636914402246475</v>
       </c>
       <c r="R15" t="n">
-        <v>0.01159264706075191</v>
+        <v>0.06843601912260056</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005780427251011133</v>
+        <v>0.01654573529958725</v>
       </c>
       <c r="T15" t="n">
-        <v>0.02745061367750168</v>
+        <v>0.0612906888127327</v>
       </c>
       <c r="U15" t="n">
-        <v>0.002099702600389719</v>
+        <v>0.01005541253834963</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01770604774355888</v>
+        <v>0.06683099269866943</v>
       </c>
       <c r="W15" t="n">
-        <v>0.005729207303375006</v>
+        <v>0.07349665462970734</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01436080131679773</v>
+        <v>0.06265745311975479</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.01960542798042297</v>
+        <v>0.002795347012579441</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.01352857518941164</v>
+        <v>0.02936345897614956</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01678444072604179</v>
+        <v>0.01405509933829308</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.001138346269726753</v>
+        <v>0.04761540144681931</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.03004193492233753</v>
+        <v>0.06862902641296387</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.00549034308642149</v>
+        <v>0.05886577814817429</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.004520478658378124</v>
+        <v>0.09439755976200104</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0006875221151858568</v>
+        <v>0.04947933554649353</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01109489891678095</v>
+        <v>0.06674247980117798</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.01765267737209797</v>
+        <v>0.07068563997745514</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.01586046256124973</v>
+        <v>0.03453612327575684</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.005574439186602831</v>
+        <v>0.0786464661359787</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.004932979587465525</v>
+        <v>0.04779576137661934</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.02765160612761974</v>
+        <v>0.07631003856658936</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0005409313598647714</v>
+        <v>0.002494494430720806</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.001435813959687948</v>
+        <v>0.1323630213737488</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.004429866559803486</v>
+        <v>0.06926731020212173</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.01009841728955507</v>
+        <v>0.08642560243606567</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.01410013996064663</v>
+        <v>0.07272009551525116</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.007372940424829721</v>
+        <v>0.04614730551838875</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.007721633184701204</v>
+        <v>0.0004139859229326248</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.01502496562898159</v>
+        <v>0.1186252981424332</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.09857319295406342</v>
+        <v>0.1813440322875977</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.007240863516926765</v>
+        <v>0.06864920258522034</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.02451174892485142</v>
+        <v>0.186467245221138</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.01964565366506577</v>
+        <v>0.1637356728315353</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.002279510023072362</v>
+        <v>0.06779250502586365</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.01491560228168964</v>
+        <v>0.013344781473279</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.004783716518431902</v>
+        <v>0.002501658163964748</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.0003703725815284997</v>
+        <v>0.1063484624028206</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.004163274541497231</v>
+        <v>0.06411328166723251</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.01295894384384155</v>
+        <v>0.02494657412171364</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.02656522579491138</v>
+        <v>0.0110961589962244</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.03374885767698288</v>
+        <v>0.06948722153902054</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.04876843467354774</v>
+        <v>0.06570124626159668</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.01355266571044922</v>
+        <v>0.006028578616678715</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.01869054511189461</v>
+        <v>0.03134453669190407</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.008062804117798805</v>
+        <v>0.05753321945667267</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.0137546407058835</v>
+        <v>0.07418139278888702</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.007279945537447929</v>
+        <v>0.04163576662540436</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.0123724490404129</v>
+        <v>0.05548867583274841</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.01315155625343323</v>
+        <v>0.04826080426573753</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.004072500858455896</v>
+        <v>0.07089053094387054</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.003320892341434956</v>
+        <v>0.01677908934652805</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01800893619656563</v>
+        <v>0.05532952770590782</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.0001774604897946119</v>
+        <v>0.05698702856898308</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.001931546488776803</v>
+        <v>0.02369950525462627</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.007248458452522755</v>
+        <v>0.002687702886760235</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.01239090319722891</v>
+        <v>0.08521100878715515</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.0580771267414093</v>
+        <v>0.2083141803741455</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.02853583544492722</v>
+        <v>0.004123743623495102</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.02298210747539997</v>
+        <v>0.1853887289762497</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.007951145060360432</v>
+        <v>0.04278948903083801</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.008853801526129246</v>
+        <v>0.1068071201443672</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.01068010367453098</v>
+        <v>0.05352677032351494</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.004905581939965487</v>
+        <v>0.008532091975212097</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.01262700650840998</v>
+        <v>0.008679848164319992</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.001484603737480938</v>
+        <v>0.004214886575937271</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.02260894514620304</v>
+        <v>0.03804092854261398</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.009196868166327477</v>
+        <v>0.03088461235165596</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.01169227156788111</v>
+        <v>0.1504948437213898</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.002228855388239026</v>
+        <v>0.001094849780201912</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.0121276006102562</v>
+        <v>0.01539703831076622</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.003102381015196443</v>
+        <v>0.005464945919811726</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.002995469840243459</v>
+        <v>0.07082110643386841</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.00775486882776022</v>
+        <v>0.009453181177377701</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.02246043086051941</v>
+        <v>0.07341037690639496</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.006208015605807304</v>
+        <v>0.0494515560567379</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.001450928626582026</v>
+        <v>0.0147235244512558</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.00455142930150032</v>
+        <v>0.2252191305160522</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.007044918369501829</v>
+        <v>0.09788099676370621</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.01182283647358418</v>
+        <v>0.04306088387966156</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.01932236365973949</v>
+        <v>0.1098261326551437</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0227708350867033</v>
+        <v>0.03827353566884995</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.004341152962297201</v>
+        <v>0.05274522677063942</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.000603546854108572</v>
+        <v>0.0127153480425477</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.01739529520273209</v>
+        <v>0.03283489868044853</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.01095972396433353</v>
+        <v>0.02862683311104774</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.01412880327552557</v>
+        <v>0.1603010296821594</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.001120814005844295</v>
+        <v>0.02837738022208214</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.01752203702926636</v>
+        <v>0.008836494758725166</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.002714552916586399</v>
+        <v>0.006831336300820112</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.002807688899338245</v>
+        <v>0.06561735272407532</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.00220589223317802</v>
+        <v>0.008824559859931469</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.01110088266432285</v>
+        <v>0.07719407975673676</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.01609619148075581</v>
+        <v>0.07878495752811432</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.006301648449152708</v>
+        <v>0.03919201716780663</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.0374898724257946</v>
+        <v>0.127973273396492</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.008056288585066795</v>
+        <v>0.02543493360280991</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.01889887452125549</v>
+        <v>0.08236555755138397</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.008573077619075775</v>
+        <v>0.007762780413031578</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.01304233819246292</v>
+        <v>0.1882316768169403</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.01218389254063368</v>
+        <v>0.01442107930779457</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.006991672329604626</v>
+        <v>0.01393439434468746</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.003296356182545424</v>
+        <v>0.06166979297995567</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.006247449666261673</v>
+        <v>0.01407079678028822</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.005339172203093767</v>
+        <v>0.04324298352003098</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.01098713092505932</v>
+        <v>0.02487420290708542</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.001949121942743659</v>
+        <v>0.07157336175441742</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.01468205079436302</v>
+        <v>0.06580532342195511</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.01254976540803909</v>
+        <v>0.00266040675342083</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.01665093004703522</v>
+        <v>0.1254919767379761</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.006272933911532164</v>
+        <v>0.02564175240695477</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.00282919337041676</v>
+        <v>0.07535851001739502</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.02279393747448921</v>
+        <v>0.09694279730319977</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.01524778641760349</v>
+        <v>0.04425564035773277</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01251131575554609</v>
+        <v>0.07023917883634567</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.008156954310834408</v>
+        <v>0.02615595050156116</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.006816809065639973</v>
+        <v>0.01144816167652607</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.00565279508009553</v>
+        <v>0.1208301186561584</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.0056024887599051</v>
+        <v>0.08384551107883453</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.005768538452684879</v>
+        <v>0.04225562140345573</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.01861247420310974</v>
+        <v>0.06335076689720154</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.01106088142842054</v>
+        <v>0.01014623045921326</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.01314481347799301</v>
+        <v>0.1387219876050949</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.009608683176338673</v>
+        <v>0.02407192438840866</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.01967719756066799</v>
+        <v>0.001610820880159736</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.003637102432549</v>
+        <v>0.01761901006102562</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.001099107321351767</v>
+        <v>0.06687496602535248</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.002160445554181933</v>
+        <v>0.002413813024759293</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.001729638082906604</v>
+        <v>0.05303433910012245</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.01022203639149666</v>
+        <v>0.06883111596107483</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.02142836339771748</v>
+        <v>0.01762408390641212</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.003353297710418701</v>
+        <v>0.1596114337444305</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.0009683428215794265</v>
+        <v>0.03291736170649529</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.02028055489063263</v>
+        <v>0.04025880619883537</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.004123566672205925</v>
+        <v>0.1071359217166901</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.01386050879955292</v>
+        <v>0.02199497446417809</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.001124697155319154</v>
+        <v>0.105112724006176</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.003243147162720561</v>
+        <v>0.01555886585265398</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.01902307383716106</v>
+        <v>0.06168709322810173</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.007244947832077742</v>
+        <v>0.02187776193022728</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.01773273944854736</v>
+        <v>0.1699424684047699</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.0008832975290715694</v>
+        <v>0.01500136684626341</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.01536236982792616</v>
+        <v>0.03024843335151672</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.003187465481460094</v>
+        <v>0.01306763663887978</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.002472281455993652</v>
+        <v>0.06494520604610443</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.00677150534465909</v>
+        <v>0.004216321744024754</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.001435171463526785</v>
+        <v>0.02744902670383453</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.01339396554976702</v>
+        <v>0.01906858198344707</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.01584929227828979</v>
+        <v>0.05714796483516693</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.008740530349314213</v>
+        <v>0.04391558840870857</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.002062655054032803</v>
+        <v>0.04732341319322586</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.01186948269605637</v>
+        <v>0.04137100279331207</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.005008550360798836</v>
+        <v>0.01966267824172974</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.0006963143241591752</v>
+        <v>0.0223715715110302</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.0006544363568536937</v>
+        <v>0.01622078195214272</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0003862683661282063</v>
+        <v>0.004796424880623817</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.02673780359327793</v>
+        <v>0.07188445329666138</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.01743373088538647</v>
+        <v>0.04579925909638405</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.0377228818833828</v>
+        <v>0.01888073980808258</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.003837804775685072</v>
+        <v>0.04082893580198288</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.01096740458160639</v>
+        <v>0.03899075835943222</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.006875541061162949</v>
+        <v>0.0777190625667572</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.01224086154252291</v>
+        <v>0.1161654219031334</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.006005024071782827</v>
+        <v>0.01287401467561722</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.02191090025007725</v>
+        <v>0.04758837819099426</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.004778156988322735</v>
+        <v>0.03197039291262627</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.003295175032690167</v>
+        <v>0.07621292769908905</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.001595960464328527</v>
+        <v>0.09854337573051453</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.001076961751095951</v>
+        <v>0.06224879994988441</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.01042021438479424</v>
+        <v>0.09047465026378632</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.05417794361710548</v>
+        <v>0.10052090883255</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.008513346314430237</v>
+        <v>0.03958531469106674</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.01392341870814562</v>
+        <v>0.06038831919431686</v>
       </c>
     </row>
     <row r="16">
